--- a/sample_data/security_financials.xlsx
+++ b/sample_data/security_financials.xlsx
@@ -16,8 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary Final Results FY26" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contracts" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FCST 9915583648 35%" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FCST 9997412455 35%" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FCST 9951761468 35%" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FCST 9978094862 35%" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FCST DeltaCorp-Supporto Securit" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary (2)" sheetId="14" state="hidden" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary (3)" sheetId="15" state="hidden" r:id="rId15"/>
@@ -8556,7 +8556,7 @@
     <row r="5">
       <c r="B5" s="264" t="inlineStr">
         <is>
-          <t>matteo.costa</t>
+          <t>noemi.rossi</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -8641,7 +8641,7 @@
     <row r="6" ht="14.15" customHeight="1" s="564">
       <c r="B6" s="264" t="inlineStr">
         <is>
-          <t>nicola.fontana</t>
+          <t>noemi.longo</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -8726,7 +8726,7 @@
     <row r="7">
       <c r="B7" s="264" t="inlineStr">
         <is>
-          <t>laura.moretti</t>
+          <t>ilaria.fontana</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -8811,7 +8811,7 @@
     <row r="8">
       <c r="B8" s="264" t="inlineStr">
         <is>
-          <t>anna.ferrari</t>
+          <t>andrea.russo</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -8896,7 +8896,7 @@
     <row r="9">
       <c r="B9" s="264" t="inlineStr">
         <is>
-          <t>stefano.santoro</t>
+          <t>martina.moretti</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -8981,7 +8981,7 @@
     <row r="10">
       <c r="B10" s="264" t="inlineStr">
         <is>
-          <t>riccardo.gentile</t>
+          <t>noemi.rinaldi</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -9066,7 +9066,7 @@
     <row r="11">
       <c r="B11" s="264" t="inlineStr">
         <is>
-          <t>fabio.ferrara</t>
+          <t>valentina.martini</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -9151,7 +9151,7 @@
     <row r="12">
       <c r="B12" s="264" t="inlineStr">
         <is>
-          <t>serena.mariani</t>
+          <t>ilaria.longo</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -9296,7 +9296,7 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>Elisa Rizzo</t>
+          <t>Tommaso Villa</t>
         </is>
       </c>
       <c r="C17" s="134" t="n">
@@ -9376,7 +9376,7 @@
       <c r="G21" s="566" t="n"/>
       <c r="H21" s="284" t="inlineStr">
         <is>
-          <t>Fabio Longo</t>
+          <t>Noemi Rossi</t>
         </is>
       </c>
       <c r="I21" s="591" t="n">
@@ -9412,10 +9412,10 @@
       <c r="G22" s="566" t="n"/>
       <c r="H22" s="286" t="inlineStr">
         <is>
-          <t>- Massimiliano Lanzi
-- Daniele Cesarano
-- Gianmarco Pappalardo
-- Alessio Manfrè</t>
+          <t>- Andrea Russo
+- Noemi Longo
+- Ilaria Fontana
+- Martina Moretti</t>
         </is>
       </c>
       <c r="I22" s="591" t="n">
@@ -9449,8 +9449,8 @@
       <c r="G23" s="566" t="n"/>
       <c r="H23" s="278" t="inlineStr">
         <is>
-          <t>- Massimo Silvestri
-- Emanuela Sebastiano</t>
+          <t>- Noemi Rinaldi
+- Valentina Martini</t>
         </is>
       </c>
       <c r="I23" s="594" t="n">
@@ -9484,8 +9484,8 @@
       <c r="G24" s="566" t="n"/>
       <c r="H24" s="278" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Massimo Silvestri
-- Emanuela Sebastiano
+          <t xml:space="preserve">- Noemi Rinaldi
+- Valentina Martini
 - 1 FTE </t>
         </is>
       </c>
@@ -9520,8 +9520,8 @@
       <c r="G25" s="566" t="n"/>
       <c r="H25" s="278" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Massimo Silvestri
-- Emanuela Sebastiano
+          <t xml:space="preserve">- Noemi Rinaldi
+- Valentina Martini
 - 2 FTE </t>
         </is>
       </c>
@@ -10450,7 +10450,7 @@
     <row r="13" ht="17.25" customHeight="1" s="564">
       <c r="A13" s="480" t="inlineStr">
         <is>
-          <t>9915583648 - BetaCredit studio accesso terze parti</t>
+          <t>9951761468 - BetaCredit studio accesso terze parti</t>
         </is>
       </c>
       <c r="H13" s="464" t="n"/>
@@ -10464,7 +10464,7 @@
     <row r="14" customFormat="1" s="469">
       <c r="A14" s="481" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="B14" s="467" t="n"/>
@@ -11168,7 +11168,7 @@
     <row r="25">
       <c r="A25" s="476" t="inlineStr">
         <is>
-          <t>9997412455 - Supporto in ambito logon</t>
+          <t>9978094862 - Supporto in ambito logon</t>
         </is>
       </c>
       <c r="B25" s="477" t="n"/>
@@ -11183,7 +11183,7 @@
     <row r="26" customFormat="1" s="469">
       <c r="A26" s="466" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="B26" s="467" t="n"/>
@@ -12119,7 +12119,7 @@
     <row r="2" ht="15" customHeight="1" s="564">
       <c r="B2" s="22" t="inlineStr">
         <is>
-          <t>martina.costa</t>
+          <t>silvia.esposito</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
@@ -12171,7 +12171,7 @@
     <row r="3">
       <c r="B3" s="22" t="inlineStr">
         <is>
-          <t>matteo.costa</t>
+          <t>noemi.rossi</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -12183,7 +12183,7 @@
       <c r="E3" s="836" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>martina.costa</t>
+          <t>silvia.esposito</t>
         </is>
       </c>
       <c r="H3" s="559" t="n"/>
@@ -12210,7 +12210,7 @@
     <row r="4">
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>nicola.fontana</t>
+          <t>noemi.longo</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -12267,7 +12267,7 @@
     <row r="5">
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>luca.leone</t>
+          <t>roberto.bianchi</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>matteo.costa</t>
+          <t>noemi.rossi</t>
         </is>
       </c>
       <c r="H5" s="559" t="n"/>
@@ -12318,7 +12318,7 @@
     <row r="6" ht="14.5" customHeight="1" s="564">
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>alberto lotito</t>
+          <t>Elena Costa</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -12375,7 +12375,7 @@
     <row r="7" ht="14.5" customHeight="1" s="564">
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>sara.rinaldi</t>
+          <t>noemi.ferrara</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -12387,7 +12387,7 @@
       <c r="E7" s="836" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>nicola.fontana</t>
+          <t>noemi.longo</t>
         </is>
       </c>
       <c r="H7" s="559" t="n"/>
@@ -12416,7 +12416,7 @@
     <row r="8" ht="14.5" customHeight="1" s="564">
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>serena.rossi</t>
+          <t>gabriele.gentile</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -12473,7 +12473,7 @@
     <row r="9">
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>matteo.romano</t>
+          <t>laura.longo</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>serena.rossi</t>
+          <t>gabriele.gentile</t>
         </is>
       </c>
       <c r="H9" s="559" t="n"/>
@@ -12514,7 +12514,7 @@
     <row r="10">
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>sara.colombo</t>
+          <t>pietro.mariani</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -12571,7 +12571,7 @@
     <row r="11">
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>stefano.greco</t>
+          <t>nicola.ferrari</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>matteo.ferrari</t>
+          <t>elena.costa</t>
         </is>
       </c>
       <c r="H11" s="559" t="n"/>
@@ -12610,7 +12610,7 @@
     <row r="12">
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>laura.moretti</t>
+          <t>ilaria.fontana</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -12663,7 +12663,7 @@
     <row r="13">
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>anna.ferrari</t>
+          <t>andrea.russo</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -12673,7 +12673,7 @@
       <c r="E13" s="836" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>matteo.romano</t>
+          <t>laura.longo</t>
         </is>
       </c>
       <c r="H13" s="559" t="n"/>
@@ -12700,7 +12700,7 @@
     <row r="14">
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>ilaria.esposito</t>
+          <t>elena.mariani</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -12753,7 +12753,7 @@
     <row r="15">
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>roberto.costa</t>
+          <t>gabriele.fontana</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -12763,7 +12763,7 @@
       <c r="E15" s="836" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>sara.colombo</t>
+          <t>pietro.mariani</t>
         </is>
       </c>
       <c r="H15" s="559" t="n"/>
@@ -12790,7 +12790,7 @@
     <row r="16">
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>ilaria.fontana</t>
+          <t>laura.gentile</t>
         </is>
       </c>
       <c r="C16" s="3" t="e">
@@ -12843,7 +12843,7 @@
     <row r="17">
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>serena.mariani</t>
+          <t>ilaria.longo</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -12853,7 +12853,7 @@
       <c r="E17" s="836" t="n"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>stefano.greco</t>
+          <t>nicola.ferrari</t>
         </is>
       </c>
       <c r="H17" s="839" t="n"/>
@@ -12878,7 +12878,7 @@
     <row r="18">
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>riccardo.gentile</t>
+          <t>noemi.rinaldi</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -12933,7 +12933,7 @@
     <row r="19">
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>fabio.ferrara</t>
+          <t>valentina.martini</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -12943,7 +12943,7 @@
       <c r="E19" s="836" t="n"/>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>sara.rinaldi</t>
+          <t>noemi.ferrara</t>
         </is>
       </c>
       <c r="H19" s="559" t="n"/>
@@ -12970,7 +12970,7 @@
     <row r="20">
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>ilaria.ferrara</t>
+          <t>tommaso.leone</t>
         </is>
       </c>
       <c r="C20" s="3" t="e">
@@ -13023,7 +13023,7 @@
     <row r="21">
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>paolo.greco</t>
+          <t>antonio.santoro</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
@@ -13052,7 +13052,7 @@
     <row r="22">
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>andrea.conti</t>
+          <t>ilaria.ferrari</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -13110,7 +13110,7 @@
       <c r="E23" s="840" t="n"/>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>laura.moretti</t>
+          <t>ilaria.fontana</t>
         </is>
       </c>
       <c r="H23" s="559" t="n">
@@ -13188,7 +13188,7 @@
       <c r="E25" s="840" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>anna.ferrari</t>
+          <t>andrea.russo</t>
         </is>
       </c>
       <c r="H25" s="559" t="n"/>
@@ -13267,7 +13267,7 @@
       <c r="D27" s="579" t="n"/>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>ilaria.esposito</t>
+          <t>elena.mariani</t>
         </is>
       </c>
       <c r="H27" s="559" t="n"/>
@@ -13345,7 +13345,7 @@
       <c r="E29" s="579" t="n"/>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>roberto.costa</t>
+          <t>gabriele.fontana</t>
         </is>
       </c>
       <c r="H29" s="559" t="n"/>
@@ -13419,7 +13419,7 @@
       <c r="D31" s="589" t="n"/>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>riccardo.gentile</t>
+          <t>noemi.rinaldi</t>
         </is>
       </c>
       <c r="H31" s="837" t="n"/>
@@ -13500,7 +13500,7 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>fabio.ferrara</t>
+          <t>valentina.martini</t>
         </is>
       </c>
       <c r="H33" s="837" t="n"/>
@@ -13570,7 +13570,7 @@
     <row r="35" hidden="1" s="564">
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>ilaria.fontana</t>
+          <t>laura.gentile</t>
         </is>
       </c>
       <c r="H35" s="559" t="n">
@@ -13636,7 +13636,7 @@
     <row r="37" hidden="1" s="564">
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>ilaria.ferrara</t>
+          <t>tommaso.leone</t>
         </is>
       </c>
       <c r="H37" s="6" t="n"/>
@@ -13700,7 +13700,7 @@
       <c r="B39" s="590" t="n"/>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>serena.mariani</t>
+          <t>ilaria.longo</t>
         </is>
       </c>
       <c r="H39" s="837" t="n"/>
@@ -13774,7 +13774,7 @@
       <c r="B41" s="590" t="n"/>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>paolo.greco</t>
+          <t>antonio.santoro</t>
         </is>
       </c>
       <c r="H41" s="837" t="n"/>
@@ -13846,7 +13846,7 @@
       <c r="B43" s="590" t="n"/>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>luca.leone</t>
+          <t>roberto.bianchi</t>
         </is>
       </c>
       <c r="H43" s="559" t="n"/>
@@ -13918,7 +13918,7 @@
       <c r="B45" s="590" t="n"/>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>andrea.conti</t>
+          <t>ilaria.ferrari</t>
         </is>
       </c>
       <c r="H45" s="837" t="n"/>
@@ -14081,7 +14081,7 @@
       <c r="B50" s="590" t="n"/>
       <c r="G50" s="27" t="inlineStr">
         <is>
-          <t>Giulia Mariani</t>
+          <t>Fabio Costa</t>
         </is>
       </c>
       <c r="H50" s="841" t="n">
@@ -14240,7 +14240,7 @@
     <row r="2" ht="15" customHeight="1" s="564">
       <c r="B2" s="22" t="inlineStr">
         <is>
-          <t>martina.costa</t>
+          <t>silvia.esposito</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
@@ -14292,7 +14292,7 @@
     <row r="3">
       <c r="B3" s="22" t="inlineStr">
         <is>
-          <t>matteo.costa</t>
+          <t>noemi.rossi</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -14304,7 +14304,7 @@
       <c r="E3" s="836" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>martina.costa</t>
+          <t>silvia.esposito</t>
         </is>
       </c>
       <c r="H3" s="559" t="n"/>
@@ -14325,7 +14325,7 @@
     <row r="4" ht="15" customHeight="1" s="564">
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>nicola.fontana</t>
+          <t>noemi.longo</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -14380,7 +14380,7 @@
     <row r="5">
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>luca.leone</t>
+          <t>roberto.bianchi</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -14394,7 +14394,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>matteo.costa</t>
+          <t>noemi.rossi</t>
         </is>
       </c>
       <c r="H5" s="559" t="n">
@@ -14423,7 +14423,7 @@
     <row r="6">
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>alberto lotito</t>
+          <t>Elena Costa</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -14480,7 +14480,7 @@
     <row r="7">
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>sara.rinaldi</t>
+          <t>noemi.ferrara</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -14492,7 +14492,7 @@
       <c r="E7" s="836" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>nicola.fontana</t>
+          <t>noemi.longo</t>
         </is>
       </c>
       <c r="H7" s="559" t="n">
@@ -14521,7 +14521,7 @@
     <row r="8">
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>serena.rossi</t>
+          <t>gabriele.gentile</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -14577,7 +14577,7 @@
     <row r="9">
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>matteo.romano</t>
+          <t>laura.longo</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>serena.rossi</t>
+          <t>gabriele.gentile</t>
         </is>
       </c>
       <c r="H9" s="559" t="n">
@@ -14622,7 +14622,7 @@
     <row r="10">
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>sara.colombo</t>
+          <t>pietro.mariani</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -14679,7 +14679,7 @@
     <row r="11">
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>stefano.greco</t>
+          <t>nicola.ferrari</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -14693,7 +14693,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>matteo.ferrari</t>
+          <t>elena.costa</t>
         </is>
       </c>
       <c r="H11" s="559" t="n">
@@ -14728,7 +14728,7 @@
     <row r="12">
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>laura.moretti</t>
+          <t>ilaria.fontana</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -14783,7 +14783,7 @@
     <row r="13">
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>anna.ferrari</t>
+          <t>andrea.russo</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -14795,7 +14795,7 @@
       <c r="E13" s="836" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>matteo.romano</t>
+          <t>laura.longo</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
@@ -14830,7 +14830,7 @@
     <row r="14">
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>ilaria.esposito</t>
+          <t>elena.mariani</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -14885,7 +14885,7 @@
     <row r="15">
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>roberto.costa</t>
+          <t>gabriele.fontana</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -14897,7 +14897,7 @@
       <c r="E15" s="836" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>sara.colombo</t>
+          <t>pietro.mariani</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
@@ -14932,7 +14932,7 @@
     <row r="16">
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>ilaria.fontana</t>
+          <t>laura.gentile</t>
         </is>
       </c>
       <c r="C16" s="3" t="e">
@@ -14987,7 +14987,7 @@
     <row r="17">
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>serena.mariani</t>
+          <t>ilaria.longo</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -14999,7 +14999,7 @@
       <c r="E17" s="5" t="n"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>stefano.greco</t>
+          <t>nicola.ferrari</t>
         </is>
       </c>
       <c r="H17" s="559" t="n">
@@ -15034,7 +15034,7 @@
     <row r="18">
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>riccardo.gentile</t>
+          <t>noemi.rinaldi</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -15089,7 +15089,7 @@
     <row r="19">
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>fabio.ferrara</t>
+          <t>valentina.martini</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -15101,7 +15101,7 @@
       <c r="E19" s="5" t="n"/>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>sara.rinaldi</t>
+          <t>noemi.ferrara</t>
         </is>
       </c>
       <c r="H19" s="559" t="n">
@@ -15128,7 +15128,7 @@
     <row r="20">
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>ilaria.ferrara</t>
+          <t>tommaso.leone</t>
         </is>
       </c>
       <c r="C20" s="3" t="e">
@@ -15183,7 +15183,7 @@
     <row r="21">
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>paolo.greco</t>
+          <t>antonio.santoro</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
@@ -15214,7 +15214,7 @@
     <row r="22">
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>andrea.conti</t>
+          <t>ilaria.ferrari</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -15269,7 +15269,7 @@
     <row r="23">
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>federica.moretti</t>
+          <t>federica.fontana</t>
         </is>
       </c>
       <c r="C23" s="3" t="e">
@@ -15281,7 +15281,7 @@
       <c r="E23" s="5" t="n"/>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>laura.moretti</t>
+          <t>ilaria.fontana</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
@@ -15316,7 +15316,7 @@
     <row r="24">
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>chiara.longo</t>
+          <t>andrea.esposito</t>
         </is>
       </c>
       <c r="C24" s="3" t="e">
@@ -15375,7 +15375,7 @@
       <c r="E25" s="579" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>anna.ferrari</t>
+          <t>andrea.russo</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
@@ -15459,7 +15459,7 @@
       <c r="E27" s="579" t="n"/>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>ilaria.esposito</t>
+          <t>elena.mariani</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
@@ -15543,7 +15543,7 @@
       <c r="E29" s="579" t="n"/>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>roberto.costa</t>
+          <t>gabriele.fontana</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
@@ -15621,7 +15621,7 @@
     <row r="31">
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>riccardo.gentile</t>
+          <t>noemi.rinaldi</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
@@ -15695,7 +15695,7 @@
     <row r="33">
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>fabio.ferrara</t>
+          <t>valentina.martini</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
@@ -15773,7 +15773,7 @@
     <row r="35" hidden="1" s="564">
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>ilaria.fontana</t>
+          <t>laura.gentile</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
@@ -15845,7 +15845,7 @@
     <row r="37" hidden="1" s="564">
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>ilaria.ferrara</t>
+          <t>tommaso.leone</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
@@ -15913,7 +15913,7 @@
     <row r="39">
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>serena.mariani</t>
+          <t>ilaria.longo</t>
         </is>
       </c>
       <c r="H39" s="837" t="n"/>
@@ -15987,7 +15987,7 @@
     <row r="41">
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>paolo.greco</t>
+          <t>antonio.santoro</t>
         </is>
       </c>
       <c r="H41" s="837" t="n"/>
@@ -16061,7 +16061,7 @@
     <row r="43">
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>luca.leone</t>
+          <t>roberto.bianchi</t>
         </is>
       </c>
       <c r="H43" s="559" t="n">
@@ -16141,7 +16141,7 @@
     <row r="45">
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>andrea.conti</t>
+          <t>ilaria.ferrari</t>
         </is>
       </c>
       <c r="H45" s="837" t="n"/>
@@ -16217,7 +16217,7 @@
     <row r="47" hidden="1" s="564">
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>federica.moretti</t>
+          <t>federica.fontana</t>
         </is>
       </c>
       <c r="H47" s="837" t="n"/>
@@ -16281,7 +16281,7 @@
     <row r="49" hidden="1" s="564">
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>chiara.longo</t>
+          <t>andrea.esposito</t>
         </is>
       </c>
       <c r="H49" s="837" t="n"/>
@@ -16436,7 +16436,7 @@
     <row r="54">
       <c r="G54" s="27" t="inlineStr">
         <is>
-          <t>Giulia Mariani</t>
+          <t>Fabio Costa</t>
         </is>
       </c>
       <c r="H54" s="841" t="n">
@@ -16575,7 +16575,7 @@
     <row r="1" ht="15" customHeight="1" s="564" thickBot="1">
       <c r="A1" s="533" t="inlineStr">
         <is>
-          <t>BYSOX001</t>
+          <t>BSOXG001</t>
         </is>
       </c>
       <c r="B1" s="24" t="inlineStr">
@@ -16602,7 +16602,7 @@
     <row r="2" ht="15" customHeight="1" s="564">
       <c r="B2" s="22" t="inlineStr">
         <is>
-          <t>martina.costa</t>
+          <t>silvia.esposito</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
@@ -16654,7 +16654,7 @@
     <row r="3" ht="15" customHeight="1" s="564">
       <c r="B3" s="22" t="inlineStr">
         <is>
-          <t>matteo.costa</t>
+          <t>noemi.rossi</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -16666,7 +16666,7 @@
       <c r="E3" s="836" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>martina.costa</t>
+          <t>silvia.esposito</t>
         </is>
       </c>
       <c r="H3" s="559" t="n"/>
@@ -16685,7 +16685,7 @@
     <row r="4" ht="15" customHeight="1" s="564">
       <c r="B4" s="22" t="inlineStr">
         <is>
-          <t>nicola.fontana</t>
+          <t>noemi.longo</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -16740,7 +16740,7 @@
     <row r="5">
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>luca.leone</t>
+          <t>roberto.bianchi</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>matteo.costa</t>
+          <t>noemi.rossi</t>
         </is>
       </c>
       <c r="H5" s="559" t="n"/>
@@ -16773,7 +16773,7 @@
     <row r="6" ht="15" customHeight="1" s="564">
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>alberto lotito</t>
+          <t>Elena Costa</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -16830,7 +16830,7 @@
     <row r="7">
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>sara.rinaldi</t>
+          <t>noemi.ferrara</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -16842,7 +16842,7 @@
       <c r="E7" s="836" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>nicola.fontana</t>
+          <t>noemi.longo</t>
         </is>
       </c>
       <c r="H7" s="559" t="n"/>
@@ -16861,7 +16861,7 @@
     <row r="8">
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>serena.rossi</t>
+          <t>gabriele.gentile</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -16916,7 +16916,7 @@
     <row r="9">
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>matteo.romano</t>
+          <t>laura.longo</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -16930,7 +16930,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>serena.rossi</t>
+          <t>gabriele.gentile</t>
         </is>
       </c>
       <c r="H9" s="559" t="n"/>
@@ -16949,7 +16949,7 @@
     <row r="10">
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>sara.colombo</t>
+          <t>pietro.mariani</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -17006,7 +17006,7 @@
     <row r="11">
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>stefano.greco</t>
+          <t>nicola.ferrari</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -17020,7 +17020,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>matteo.ferrari</t>
+          <t>elena.costa</t>
         </is>
       </c>
       <c r="H11" s="559" t="n"/>
@@ -17061,7 +17061,7 @@
     <row r="12">
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>laura.moretti</t>
+          <t>ilaria.fontana</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -17114,7 +17114,7 @@
     <row r="13">
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>anna.ferrari</t>
+          <t>andrea.russo</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -17124,7 +17124,7 @@
       <c r="E13" s="836" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>matteo.romano</t>
+          <t>laura.longo</t>
         </is>
       </c>
       <c r="H13" s="559" t="n"/>
@@ -17143,7 +17143,7 @@
     <row r="14">
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>ilaria.esposito</t>
+          <t>elena.mariani</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -17196,7 +17196,7 @@
     <row r="15">
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>roberto.costa</t>
+          <t>gabriele.fontana</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -17206,7 +17206,7 @@
       <c r="E15" s="836" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>sara.colombo</t>
+          <t>pietro.mariani</t>
         </is>
       </c>
       <c r="H15" s="559" t="n"/>
@@ -17225,7 +17225,7 @@
     <row r="16">
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>ilaria.fontana</t>
+          <t>laura.gentile</t>
         </is>
       </c>
       <c r="C16" s="3" t="e">
@@ -17278,7 +17278,7 @@
     <row r="17">
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>serena.mariani</t>
+          <t>ilaria.longo</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -17288,7 +17288,7 @@
       <c r="E17" s="5" t="n"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>stefano.greco</t>
+          <t>nicola.ferrari</t>
         </is>
       </c>
       <c r="H17" s="559" t="n"/>
@@ -17307,7 +17307,7 @@
     <row r="18">
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>riccardo.gentile</t>
+          <t>noemi.rinaldi</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -17360,7 +17360,7 @@
     <row r="19">
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>fabio.ferrara</t>
+          <t>valentina.martini</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -17370,7 +17370,7 @@
       <c r="E19" s="5" t="n"/>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>sara.rinaldi</t>
+          <t>noemi.ferrara</t>
         </is>
       </c>
       <c r="H19" s="559" t="n"/>
@@ -17389,7 +17389,7 @@
     <row r="20">
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>ilaria.ferrara</t>
+          <t>tommaso.leone</t>
         </is>
       </c>
       <c r="C20" s="3" t="e">
@@ -17442,7 +17442,7 @@
     <row r="21">
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>paolo.greco</t>
+          <t>antonio.santoro</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
@@ -17471,7 +17471,7 @@
     <row r="22">
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>andrea.conti</t>
+          <t>ilaria.ferrari</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -17528,7 +17528,7 @@
       <c r="E23" s="840" t="n"/>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>laura.moretti</t>
+          <t>ilaria.fontana</t>
         </is>
       </c>
       <c r="H23" s="559" t="n"/>
@@ -17584,7 +17584,7 @@
       <c r="E25" s="840" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>anna.ferrari</t>
+          <t>andrea.russo</t>
         </is>
       </c>
       <c r="H25" s="559" t="n"/>
@@ -17640,7 +17640,7 @@
       <c r="E27" s="840" t="n"/>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>ilaria.esposito</t>
+          <t>elena.mariani</t>
         </is>
       </c>
       <c r="H27" s="559" t="n"/>
@@ -17696,7 +17696,7 @@
       <c r="E29" s="840" t="n"/>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>roberto.costa</t>
+          <t>gabriele.fontana</t>
         </is>
       </c>
       <c r="H29" s="559" t="n"/>
@@ -17752,7 +17752,7 @@
       <c r="E31" s="840" t="n"/>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>riccardo.gentile</t>
+          <t>noemi.rinaldi</t>
         </is>
       </c>
       <c r="H31" s="559" t="n"/>
@@ -17807,7 +17807,7 @@
       <c r="E33" s="840" t="n"/>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>fabio.ferrara</t>
+          <t>valentina.martini</t>
         </is>
       </c>
       <c r="H33" s="559" t="n"/>
@@ -17859,7 +17859,7 @@
     <row r="35" hidden="1" s="564">
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>ilaria.fontana</t>
+          <t>laura.gentile</t>
         </is>
       </c>
       <c r="H35" s="559" t="n"/>
@@ -17907,7 +17907,7 @@
     <row r="37" hidden="1" s="564">
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>ilaria.ferrara</t>
+          <t>tommaso.leone</t>
         </is>
       </c>
       <c r="H37" s="559" t="n"/>
@@ -17955,7 +17955,7 @@
     <row r="39" hidden="1" s="564">
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>serena.mariani</t>
+          <t>ilaria.longo</t>
         </is>
       </c>
       <c r="H39" s="838" t="n"/>
@@ -18003,7 +18003,7 @@
     <row r="41" hidden="1" s="564">
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>paolo.greco</t>
+          <t>antonio.santoro</t>
         </is>
       </c>
       <c r="H41" s="838" t="n"/>
@@ -18051,7 +18051,7 @@
     <row r="43" hidden="1" s="564">
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>luca.leone</t>
+          <t>roberto.bianchi</t>
         </is>
       </c>
       <c r="H43" s="838" t="n"/>
@@ -18113,7 +18113,7 @@
     <row r="45">
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>ilaria.esposito</t>
+          <t>elena.mariani</t>
         </is>
       </c>
       <c r="H45" s="559" t="n"/>
@@ -18264,7 +18264,7 @@
     <row r="50">
       <c r="G50" s="27" t="inlineStr">
         <is>
-          <t>Giulia Mariani</t>
+          <t>Fabio Costa</t>
         </is>
       </c>
       <c r="H50" s="842" t="n">
@@ -18827,12 +18827,12 @@
       </c>
       <c r="B4" s="696" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="C4" s="696" t="inlineStr">
         <is>
-          <t>BFBZ3001</t>
+          <t>BBZ3U001</t>
         </is>
       </c>
       <c r="D4" s="688" t="n"/>
@@ -18992,12 +18992,12 @@
       </c>
       <c r="B5" s="696" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="C5" s="696" t="inlineStr">
         <is>
-          <t>BU7R5001</t>
+          <t>B7R5Y001</t>
         </is>
       </c>
       <c r="D5" s="688" t="n"/>
@@ -19792,11 +19792,11 @@
         </is>
       </c>
       <c r="D10" s="36" t="n">
-        <v>9915583648</v>
+        <v>9951761468</v>
       </c>
       <c r="E10" s="35" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="F10" s="35" t="inlineStr">
@@ -20780,11 +20780,11 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>9997412455</v>
+        <v>9978094862</v>
       </c>
       <c r="E17" s="35" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="F17" s="35" t="inlineStr">
@@ -21819,7 +21819,7 @@
       <c r="D24" s="36" t="n"/>
       <c r="E24" s="35" t="inlineStr">
         <is>
-          <t>BYSOX001</t>
+          <t>BSOXG001</t>
         </is>
       </c>
       <c r="F24" s="191" t="inlineStr">
@@ -22458,12 +22458,12 @@
       </c>
       <c r="B4" s="696" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="C4" s="696" t="inlineStr">
         <is>
-          <t>BFBZ3001</t>
+          <t>BBZ3U001</t>
         </is>
       </c>
       <c r="D4" s="688" t="n"/>
@@ -22621,12 +22621,12 @@
       </c>
       <c r="B5" s="696" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="C5" s="696" t="inlineStr">
         <is>
-          <t>BU7R5001</t>
+          <t>B7R5Y001</t>
         </is>
       </c>
       <c r="D5" s="688" t="n"/>
@@ -23421,11 +23421,11 @@
         </is>
       </c>
       <c r="D10" s="36" t="n">
-        <v>9915583648</v>
+        <v>9951761468</v>
       </c>
       <c r="E10" s="35" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="F10" s="35" t="inlineStr">
@@ -24437,11 +24437,11 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>9997412455</v>
+        <v>9978094862</v>
       </c>
       <c r="E17" s="35" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="F17" s="35" t="inlineStr">
@@ -25476,7 +25476,7 @@
       <c r="D24" s="36" t="n"/>
       <c r="E24" s="35" t="inlineStr">
         <is>
-          <t>BYSOX001</t>
+          <t>BSOXG001</t>
         </is>
       </c>
       <c r="F24" s="191" t="inlineStr">
@@ -26134,7 +26134,7 @@
     <row r="3" hidden="1" s="564">
       <c r="B3" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C3" s="574" t="inlineStr">
@@ -26157,7 +26157,7 @@
       <c r="H3" s="574" t="n"/>
       <c r="I3" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="J3" s="579" t="inlineStr">
@@ -26182,7 +26182,7 @@
       </c>
       <c r="Q3" s="560" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="R3" s="597" t="n">
@@ -26192,7 +26192,7 @@
     <row r="4" hidden="1" ht="130.5" customHeight="1" s="564">
       <c r="B4" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C4" s="574" t="inlineStr">
@@ -26212,7 +26212,7 @@
       </c>
       <c r="F4" s="574" t="inlineStr">
         <is>
-          <t>2193039517</t>
+          <t>7655399741</t>
         </is>
       </c>
       <c r="G4" s="574" t="n"/>
@@ -26231,7 +26231,7 @@
       </c>
       <c r="I4" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="J4" s="579" t="inlineStr">
@@ -26241,7 +26241,7 @@
       </c>
       <c r="K4" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="L4" s="580" t="n"/>
@@ -26261,7 +26261,7 @@
       </c>
       <c r="Q4" s="560" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="R4" s="597" t="n">
@@ -26271,7 +26271,7 @@
     <row r="5" hidden="1" ht="159.5" customHeight="1" s="564">
       <c r="B5" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C5" s="574" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="F5" s="574" t="inlineStr">
         <is>
-          <t>5783765539</t>
+          <t>0568288132</t>
         </is>
       </c>
       <c r="G5" s="574" t="n"/>
@@ -26308,7 +26308,7 @@
       </c>
       <c r="I5" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="J5" s="579" t="inlineStr">
@@ -26318,7 +26318,7 @@
       </c>
       <c r="K5" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="L5" s="580" t="n"/>
@@ -26348,7 +26348,7 @@
     <row r="6" hidden="1" s="564">
       <c r="B6" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C6" s="574" t="inlineStr">
@@ -26371,7 +26371,7 @@
       <c r="H6" s="574" t="n"/>
       <c r="I6" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="J6" s="579" t="inlineStr">
@@ -26398,7 +26398,7 @@
     <row r="7">
       <c r="B7" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C7" s="574" t="inlineStr">
@@ -26418,7 +26418,7 @@
       </c>
       <c r="F7" s="574" t="inlineStr">
         <is>
-          <t>1056828813</t>
+          <t>5791516980</t>
         </is>
       </c>
       <c r="G7" s="574" t="inlineStr">
@@ -26428,12 +26428,12 @@
       </c>
       <c r="H7" s="574" t="inlineStr">
         <is>
-          <t>2780948625</t>
+          <t>2189060013</t>
         </is>
       </c>
       <c r="I7" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="J7" s="579" t="inlineStr">
@@ -26443,7 +26443,7 @@
       </c>
       <c r="K7" s="579" t="inlineStr">
         <is>
-          <t>Stefano Rinaldi</t>
+          <t>Aurora Santoro</t>
         </is>
       </c>
       <c r="L7" s="580" t="n"/>
@@ -26465,7 +26465,7 @@
     <row r="8">
       <c r="B8" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C8" s="574" t="inlineStr">
@@ -26485,7 +26485,7 @@
       </c>
       <c r="F8" s="574" t="inlineStr">
         <is>
-          <t>1056828813</t>
+          <t>5791516980</t>
         </is>
       </c>
       <c r="G8" s="574" t="inlineStr">
@@ -26494,11 +26494,11 @@
         </is>
       </c>
       <c r="H8" s="560" t="n">
-        <v>1516980218</v>
+        <v>7674098591</v>
       </c>
       <c r="I8" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="J8" s="579" t="inlineStr">
@@ -26508,7 +26508,7 @@
       </c>
       <c r="K8" s="579" t="inlineStr">
         <is>
-          <t>Stefano Rinaldi</t>
+          <t>Aurora Santoro</t>
         </is>
       </c>
       <c r="L8" s="580" t="n"/>
@@ -26529,7 +26529,7 @@
     </row>
     <row r="9">
       <c r="B9" s="574" t="n">
-        <v>9997412455</v>
+        <v>9978094862</v>
       </c>
       <c r="C9" s="574" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
       </c>
       <c r="F9" s="574" t="inlineStr">
         <is>
-          <t>9060013876</t>
+          <t>7317984193</t>
         </is>
       </c>
       <c r="G9" s="579" t="inlineStr">
@@ -26558,12 +26558,12 @@
       </c>
       <c r="H9" s="574" t="inlineStr">
         <is>
-          <t>7409859173</t>
+          <t>0515213978</t>
         </is>
       </c>
       <c r="I9" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="J9" s="579" t="inlineStr">
@@ -26573,7 +26573,7 @@
       </c>
       <c r="K9" s="579" t="inlineStr">
         <is>
-          <t>Sara Longo</t>
+          <t>Riccardo Gentile</t>
         </is>
       </c>
       <c r="L9" s="580" t="n"/>
@@ -26594,7 +26594,7 @@
     </row>
     <row r="10">
       <c r="B10" s="574" t="n">
-        <v>9997412455</v>
+        <v>9978094862</v>
       </c>
       <c r="C10" s="574" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
       </c>
       <c r="F10" s="574" t="inlineStr">
         <is>
-          <t>7984193051</t>
+          <t>6454877766</t>
         </is>
       </c>
       <c r="G10" s="579" t="inlineStr">
@@ -26623,12 +26623,12 @@
       </c>
       <c r="H10" s="574" t="inlineStr">
         <is>
-          <t>5213978964</t>
+          <t>3465952776</t>
         </is>
       </c>
       <c r="I10" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="J10" s="579" t="inlineStr">
@@ -26638,7 +26638,7 @@
       </c>
       <c r="K10" s="579" t="inlineStr">
         <is>
-          <t>Stefano Rinaldi</t>
+          <t>Aurora Santoro</t>
         </is>
       </c>
       <c r="L10" s="580" t="n"/>
@@ -26659,7 +26659,7 @@
     </row>
     <row r="11">
       <c r="B11" s="574" t="n">
-        <v>9997412455</v>
+        <v>9978094862</v>
       </c>
       <c r="C11" s="574" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="F11" s="574" t="inlineStr">
         <is>
-          <t>5487776634</t>
+          <t>1074077198</t>
         </is>
       </c>
       <c r="G11" s="579" t="inlineStr">
@@ -26687,11 +26687,11 @@
         </is>
       </c>
       <c r="H11" s="574" t="n">
-        <v>6595277610</v>
+        <v>4404248011</v>
       </c>
       <c r="I11" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="J11" s="579" t="inlineStr">
@@ -26701,7 +26701,7 @@
       </c>
       <c r="K11" s="579" t="inlineStr">
         <is>
-          <t>Stefano Rinaldi</t>
+          <t>Aurora Santoro</t>
         </is>
       </c>
       <c r="L11" s="580" t="n"/>
@@ -26722,7 +26722,7 @@
     </row>
     <row r="12">
       <c r="B12" s="574" t="n">
-        <v>9997412455</v>
+        <v>9978094862</v>
       </c>
       <c r="C12" s="574" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
       </c>
       <c r="F12" s="574" t="inlineStr">
         <is>
-          <t>7407719844</t>
+          <t>9062761926</t>
         </is>
       </c>
       <c r="G12" s="574" t="inlineStr">
@@ -26751,12 +26751,12 @@
       </c>
       <c r="H12" s="574" t="inlineStr">
         <is>
-          <t>0424801190</t>
+          <t>9353979457</t>
         </is>
       </c>
       <c r="I12" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="J12" s="579" t="inlineStr">
@@ -26766,7 +26766,7 @@
       </c>
       <c r="K12" s="579" t="inlineStr">
         <is>
-          <t>Stefano Rinaldi</t>
+          <t>Aurora Santoro</t>
         </is>
       </c>
       <c r="L12" s="580" t="n"/>
@@ -26788,7 +26788,7 @@
     <row r="13" hidden="1" s="564">
       <c r="B13" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C13" s="574" t="inlineStr">
@@ -26808,7 +26808,7 @@
       </c>
       <c r="F13" s="574" t="inlineStr">
         <is>
-          <t>6276192693</t>
+          <t>2966451835</t>
         </is>
       </c>
       <c r="G13" s="574" t="n"/>
@@ -26819,7 +26819,7 @@
       </c>
       <c r="I13" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="J13" s="579" t="inlineStr">
@@ -26829,7 +26829,7 @@
       </c>
       <c r="K13" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="L13" s="580" t="n"/>
@@ -26851,7 +26851,7 @@
     <row r="14" hidden="1" s="564">
       <c r="B14" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C14" s="574" t="inlineStr">
@@ -26871,7 +26871,7 @@
       </c>
       <c r="F14" s="574" t="inlineStr">
         <is>
-          <t>5397945729</t>
+          <t>1313876218</t>
         </is>
       </c>
       <c r="G14" s="574" t="n"/>
@@ -26882,7 +26882,7 @@
       </c>
       <c r="I14" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="J14" s="579" t="inlineStr">
@@ -26892,7 +26892,7 @@
       </c>
       <c r="K14" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="L14" s="580" t="n"/>
@@ -26914,7 +26914,7 @@
     <row r="15" hidden="1" s="564">
       <c r="B15" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C15" s="574" t="inlineStr">
@@ -26934,7 +26934,7 @@
       </c>
       <c r="F15" s="574" t="inlineStr">
         <is>
-          <t>6645183513</t>
+          <t>2434733955</t>
         </is>
       </c>
       <c r="G15" s="574" t="n"/>
@@ -26945,7 +26945,7 @@
       </c>
       <c r="I15" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="J15" s="579" t="inlineStr">
@@ -26955,7 +26955,7 @@
       </c>
       <c r="K15" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="L15" s="580" t="n"/>
@@ -26980,7 +26980,7 @@
     <row r="16" hidden="1" s="564">
       <c r="B16" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C16" s="574" t="inlineStr">
@@ -27000,7 +27000,7 @@
       </c>
       <c r="F16" s="574" t="inlineStr">
         <is>
-          <t>1387621824</t>
+          <t>2661596084</t>
         </is>
       </c>
       <c r="G16" s="574" t="n"/>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="I16" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="J16" s="579" t="inlineStr">
@@ -27021,7 +27021,7 @@
       </c>
       <c r="K16" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="L16" s="580" t="n"/>
@@ -27043,7 +27043,7 @@
     <row r="17" hidden="1" ht="28" customHeight="1" s="564">
       <c r="B17" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C17" s="574" t="inlineStr">
@@ -27063,7 +27063,7 @@
       </c>
       <c r="F17" s="574" t="inlineStr">
         <is>
-          <t>3473395526</t>
+          <t>1300068553</t>
         </is>
       </c>
       <c r="G17" s="574" t="n"/>
@@ -27074,7 +27074,7 @@
       </c>
       <c r="I17" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="J17" s="579" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="K17" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="L17" s="580" t="n"/>
@@ -27103,13 +27103,13 @@
         </is>
       </c>
       <c r="Q17" s="579" t="n">
-        <v>6159608413</v>
+        <v>6141172536</v>
       </c>
     </row>
     <row r="18" hidden="1" s="564">
       <c r="B18" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C18" s="574" t="inlineStr">
@@ -27129,7 +27129,7 @@
       </c>
       <c r="F18" s="574" t="inlineStr">
         <is>
-          <t>0006855361</t>
+          <t>4210402274</t>
         </is>
       </c>
       <c r="G18" s="574" t="n"/>
@@ -27140,7 +27140,7 @@
       </c>
       <c r="I18" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="J18" s="579" t="inlineStr">
@@ -27150,7 +27150,7 @@
       </c>
       <c r="K18" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="L18" s="580" t="n"/>
@@ -27169,12 +27169,12 @@
         </is>
       </c>
       <c r="Q18" s="579" t="n">
-        <v>4117253642</v>
+        <v>5830268678</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="574" t="n">
-        <v>9997412455</v>
+        <v>9978094862</v>
       </c>
       <c r="C19" s="574" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
       </c>
       <c r="F19" s="574" t="inlineStr">
         <is>
-          <t>1040227458</t>
+          <t>9519731624</t>
         </is>
       </c>
       <c r="G19" s="574" t="inlineStr">
@@ -27203,12 +27203,12 @@
       </c>
       <c r="H19" s="574" t="inlineStr">
         <is>
-          <t>3026867895</t>
+          <t>7520068346</t>
         </is>
       </c>
       <c r="I19" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="J19" s="130" t="inlineStr">
@@ -27218,7 +27218,7 @@
       </c>
       <c r="K19" s="130" t="inlineStr">
         <is>
-          <t>Serena Ferrari</t>
+          <t>Anna Leone</t>
         </is>
       </c>
       <c r="L19" s="132" t="n"/>
@@ -27240,7 +27240,7 @@
     <row r="20">
       <c r="B20" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C20" s="574" t="inlineStr">
@@ -27260,7 +27260,7 @@
       </c>
       <c r="F20" s="574" t="inlineStr">
         <is>
-          <t>9731624752</t>
+          <t>2044538361</t>
         </is>
       </c>
       <c r="G20" s="574" t="inlineStr">
@@ -27270,12 +27270,12 @@
       </c>
       <c r="H20" s="574" t="inlineStr">
         <is>
-          <t>0068346720</t>
+          <t>2719012962</t>
         </is>
       </c>
       <c r="I20" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="J20" s="579" t="inlineStr">
@@ -27306,7 +27306,7 @@
     </row>
     <row r="21" hidden="1" ht="29" customHeight="1" s="564">
       <c r="B21" s="560" t="n">
-        <v>9944538361</v>
+        <v>9956730029</v>
       </c>
       <c r="C21" s="574" t="inlineStr">
         <is>
@@ -27337,12 +27337,12 @@
       </c>
       <c r="J21" s="579" t="inlineStr">
         <is>
-          <t>Chiara Barbieri</t>
+          <t>Cristina Colombo</t>
         </is>
       </c>
       <c r="K21" s="579" t="inlineStr">
         <is>
-          <t>Stefano Rinaldi</t>
+          <t>Aurora Santoro</t>
         </is>
       </c>
       <c r="L21" s="580" t="inlineStr">
@@ -27369,7 +27369,7 @@
     <row r="22" hidden="1" ht="58.5" customHeight="1" s="564">
       <c r="B22" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C22" s="574" t="inlineStr">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="F22" s="574" t="inlineStr">
         <is>
-          <t>3473395526</t>
+          <t>1300068553</t>
         </is>
       </c>
       <c r="G22" s="574" t="n"/>
@@ -27400,7 +27400,7 @@
       </c>
       <c r="I22" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="J22" s="579" t="inlineStr">
@@ -27410,7 +27410,7 @@
       </c>
       <c r="K22" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="L22" s="580" t="n"/>
@@ -27429,13 +27429,13 @@
         </is>
       </c>
       <c r="Q22" s="579" t="n">
-        <v>1901296256</v>
+        <v>1503455261</v>
       </c>
     </row>
     <row r="23" ht="29" customHeight="1" s="564">
       <c r="B23" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C23" s="574" t="inlineStr">
@@ -27455,7 +27455,7 @@
       </c>
       <c r="F23" s="574" t="inlineStr">
         <is>
-          <t>7300291503</t>
+          <t>8405386334</t>
         </is>
       </c>
       <c r="G23" s="574" t="inlineStr">
@@ -27465,12 +27465,12 @@
       </c>
       <c r="H23" s="574" t="inlineStr">
         <is>
-          <t>4552618405</t>
+          <t>9334577096</t>
         </is>
       </c>
       <c r="I23" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="J23" s="574" t="inlineStr">
@@ -27480,7 +27480,7 @@
       </c>
       <c r="K23" s="579" t="inlineStr">
         <is>
-          <t>Stefano Rinaldi</t>
+          <t>Aurora Santoro</t>
         </is>
       </c>
       <c r="L23" s="580" t="inlineStr">
@@ -27503,12 +27503,12 @@
         </is>
       </c>
       <c r="Q23" s="579" t="n">
-        <v>3863349334</v>
+        <v>8277566712</v>
       </c>
     </row>
     <row r="24" ht="29" customHeight="1" s="564">
       <c r="B24" s="574" t="n">
-        <v>9997412455</v>
+        <v>9978094862</v>
       </c>
       <c r="C24" s="574" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
       </c>
       <c r="F24" s="574" t="inlineStr">
         <is>
-          <t>5770968277</t>
+          <t>7887556341</t>
         </is>
       </c>
       <c r="G24" s="574" t="inlineStr">
@@ -27537,12 +27537,12 @@
       </c>
       <c r="H24" s="574" t="inlineStr">
         <is>
-          <t>5667127887</t>
+          <t>7389455465</t>
         </is>
       </c>
       <c r="I24" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="J24" s="579" t="inlineStr">
@@ -27552,7 +27552,7 @@
       </c>
       <c r="K24" s="579" t="inlineStr">
         <is>
-          <t>Stefano Rinaldi</t>
+          <t>Aurora Santoro</t>
         </is>
       </c>
       <c r="L24" s="580" t="inlineStr">
@@ -27575,13 +27575,13 @@
         </is>
       </c>
       <c r="Q24" s="579" t="n">
-        <v>5563417389</v>
+        <v>6210599302</v>
       </c>
     </row>
     <row r="25" ht="29" customHeight="1" s="564">
       <c r="B25" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C25" s="574" t="inlineStr">
@@ -27601,7 +27601,7 @@
       </c>
       <c r="F25" s="574" t="inlineStr">
         <is>
-          <t>4554656210</t>
+          <t>5023778876</t>
         </is>
       </c>
       <c r="G25" s="574" t="inlineStr">
@@ -27611,12 +27611,12 @@
       </c>
       <c r="H25" s="574" t="inlineStr">
         <is>
-          <t>5993025023</t>
+          <t>0317439418</t>
         </is>
       </c>
       <c r="I25" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="J25" s="579" t="inlineStr">
@@ -27626,7 +27626,7 @@
       </c>
       <c r="K25" s="579" t="inlineStr">
         <is>
-          <t>Serena Ferrari</t>
+          <t>Anna Leone</t>
         </is>
       </c>
       <c r="L25" s="580" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="26" ht="130" customHeight="1" s="564">
       <c r="B26" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C26" s="574" t="inlineStr">
@@ -27672,7 +27672,7 @@
       </c>
       <c r="F26" s="574" t="inlineStr">
         <is>
-          <t>7788760317</t>
+          <t>9274305476</t>
         </is>
       </c>
       <c r="G26" s="574" t="inlineStr">
@@ -27682,12 +27682,12 @@
       </c>
       <c r="H26" s="574" t="inlineStr">
         <is>
-          <t>4394189274</t>
+          <t>2930079869</t>
         </is>
       </c>
       <c r="I26" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="J26" s="579" t="inlineStr">
@@ -27697,7 +27697,7 @@
       </c>
       <c r="K26" s="579" t="inlineStr">
         <is>
-          <t>Elisa Conti</t>
+          <t>Silvia Russo</t>
         </is>
       </c>
       <c r="L26" s="580" t="inlineStr">
@@ -27735,7 +27735,7 @@
     <row r="27">
       <c r="B27" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C27" s="574" t="inlineStr">
@@ -27755,22 +27755,22 @@
       </c>
       <c r="F27" s="574" t="inlineStr">
         <is>
-          <t>0547629300</t>
+          <t>3444723518</t>
         </is>
       </c>
       <c r="G27" s="574" t="inlineStr">
         <is>
-          <t>79869</t>
+          <t>33732</t>
         </is>
       </c>
       <c r="H27" s="574" t="inlineStr">
         <is>
-          <t>6134447235</t>
+          <t>5478682050</t>
         </is>
       </c>
       <c r="I27" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="J27" s="579" t="inlineStr">
@@ -27780,7 +27780,7 @@
       </c>
       <c r="K27" s="579" t="inlineStr">
         <is>
-          <t>Stefano Rinaldi</t>
+          <t>Aurora Santoro</t>
         </is>
       </c>
       <c r="L27" s="580" t="inlineStr">
@@ -27803,14 +27803,14 @@
         </is>
       </c>
       <c r="Q27" s="220" t="n">
-        <v>1833732547</v>
+        <v>6388090253</v>
       </c>
       <c r="R27" s="597" t="n"/>
     </row>
     <row r="28" hidden="1" ht="14.5" customHeight="1" s="564">
       <c r="B28" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C28" s="574" t="inlineStr">
@@ -27826,7 +27826,7 @@
       <c r="E28" s="574" t="n"/>
       <c r="F28" s="574" t="inlineStr">
         <is>
-          <t>8682050638</t>
+          <t>5584155952</t>
         </is>
       </c>
       <c r="G28" s="129" t="n"/>
@@ -27837,7 +27837,7 @@
       </c>
       <c r="I28" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="J28" s="579" t="inlineStr">
@@ -27847,7 +27847,7 @@
       </c>
       <c r="K28" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="L28" s="580" t="inlineStr">
@@ -27874,7 +27874,7 @@
     <row r="29" hidden="1" ht="29" customHeight="1" s="564">
       <c r="B29" s="574" t="inlineStr">
         <is>
-          <t>9944538361</t>
+          <t>9956730029</t>
         </is>
       </c>
       <c r="C29" s="574" t="inlineStr">
@@ -27896,7 +27896,7 @@
       </c>
       <c r="H29" s="574" t="inlineStr">
         <is>
-          <t>8090253558</t>
+          <t>5140278709</t>
         </is>
       </c>
       <c r="I29" s="579" t="inlineStr">
@@ -27911,7 +27911,7 @@
       </c>
       <c r="K29" s="579" t="inlineStr">
         <is>
-          <t>Stefano Rinaldi</t>
+          <t>Aurora Santoro</t>
         </is>
       </c>
       <c r="L29" s="580" t="inlineStr">
@@ -27937,7 +27937,7 @@
     <row r="30" hidden="1" ht="78" customHeight="1" s="564">
       <c r="B30" s="574" t="inlineStr">
         <is>
-          <t>9944538361</t>
+          <t>9956730029</t>
         </is>
       </c>
       <c r="C30" s="574" t="inlineStr">
@@ -27959,7 +27959,7 @@
       </c>
       <c r="H30" s="574" t="inlineStr">
         <is>
-          <t>4155952514</t>
+          <t>5073225446</t>
         </is>
       </c>
       <c r="I30" s="579" t="inlineStr">
@@ -27974,7 +27974,7 @@
       </c>
       <c r="K30" s="579" t="inlineStr">
         <is>
-          <t>Luca Vitale</t>
+          <t>Valentina Santoro</t>
         </is>
       </c>
       <c r="L30" s="580" t="inlineStr">
@@ -28000,7 +28000,7 @@
     <row r="31" hidden="1" ht="29" customHeight="1" s="564">
       <c r="B31" s="574" t="inlineStr">
         <is>
-          <t>9944538361</t>
+          <t>9956730029</t>
         </is>
       </c>
       <c r="C31" s="574" t="inlineStr">
@@ -28039,7 +28039,7 @@
       </c>
       <c r="K31" s="579" t="inlineStr">
         <is>
-          <t>Andrea Leone</t>
+          <t>Sara Russo</t>
         </is>
       </c>
       <c r="L31" s="580" t="inlineStr">
@@ -28060,7 +28060,7 @@
     </row>
     <row r="32" hidden="1" ht="72.5" customHeight="1" s="564">
       <c r="B32" s="574" t="n">
-        <v>9915583648</v>
+        <v>9951761468</v>
       </c>
       <c r="C32" s="580" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
       </c>
       <c r="F32" s="574" t="inlineStr">
         <is>
-          <t>7870950732</t>
+          <t>4726767434</t>
         </is>
       </c>
       <c r="G32" s="580" t="n"/>
@@ -28090,7 +28090,7 @@
       </c>
       <c r="I32" s="580" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="J32" s="580" t="inlineStr">
@@ -28100,7 +28100,7 @@
       </c>
       <c r="K32" s="580" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="L32" s="580" t="inlineStr">
@@ -28126,7 +28126,7 @@
     </row>
     <row r="33" hidden="1" ht="58" customHeight="1" s="564">
       <c r="B33" s="574" t="n">
-        <v>9915583648</v>
+        <v>9951761468</v>
       </c>
       <c r="C33" s="574" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
       </c>
       <c r="F33" s="574" t="inlineStr">
         <is>
-          <t>2544658114</t>
+          <t>9010730268</t>
         </is>
       </c>
       <c r="G33" s="574" t="n"/>
@@ -28156,7 +28156,7 @@
       </c>
       <c r="I33" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="J33" s="579" t="inlineStr">
@@ -28166,7 +28166,7 @@
       </c>
       <c r="K33" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="L33" s="580" t="inlineStr">
@@ -28201,7 +28201,7 @@
     <row r="34" hidden="1" ht="43.5" customHeight="1" s="564">
       <c r="B34" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C34" s="574" t="inlineStr">
@@ -28221,7 +28221,7 @@
       </c>
       <c r="F34" s="574" t="inlineStr">
         <is>
-          <t>7267674349</t>
+          <t>8475906685</t>
         </is>
       </c>
       <c r="G34" s="129" t="n"/>
@@ -28232,7 +28232,7 @@
       </c>
       <c r="I34" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="J34" s="579" t="inlineStr">
@@ -28242,7 +28242,7 @@
       </c>
       <c r="K34" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="L34" s="580" t="inlineStr">
@@ -28277,7 +28277,7 @@
     <row r="35" hidden="1" s="564">
       <c r="B35" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C35" s="574" t="inlineStr">
@@ -28297,7 +28297,7 @@
       </c>
       <c r="F35" s="574" t="inlineStr">
         <is>
-          <t>0107302688</t>
+          <t>5336793687</t>
         </is>
       </c>
       <c r="G35" s="129" t="n"/>
@@ -28308,7 +28308,7 @@
       </c>
       <c r="I35" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="J35" s="579" t="inlineStr">
@@ -28318,7 +28318,7 @@
       </c>
       <c r="K35" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="L35" s="580" t="inlineStr">
@@ -28341,13 +28341,13 @@
         </is>
       </c>
       <c r="Q35" s="560" t="n">
-        <v>4759066855</v>
+        <v>3021849040</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C36" s="574" t="inlineStr">
@@ -28367,22 +28367,22 @@
       </c>
       <c r="F36" s="574" t="inlineStr">
         <is>
-          <t>3367936873</t>
+          <t>9224297388</t>
         </is>
       </c>
       <c r="G36" s="574" t="inlineStr">
         <is>
-          <t>02184</t>
+          <t>72777</t>
         </is>
       </c>
       <c r="H36" s="574" t="inlineStr">
         <is>
-          <t>9040922429</t>
+          <t>6627502184</t>
         </is>
       </c>
       <c r="I36" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -28392,7 +28392,7 @@
       </c>
       <c r="K36" s="579" t="inlineStr">
         <is>
-          <t>Stefano Rinaldi</t>
+          <t>Aurora Santoro</t>
         </is>
       </c>
       <c r="L36" s="580" t="inlineStr">
@@ -28415,13 +28415,13 @@
         </is>
       </c>
       <c r="Q36" s="246" t="n">
-        <v>7388727776</v>
+        <v>8564547077</v>
       </c>
     </row>
     <row r="37" hidden="1" s="564">
       <c r="B37" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C37" s="574" t="inlineStr">
@@ -28441,7 +28441,7 @@
       </c>
       <c r="F37" s="574" t="inlineStr">
         <is>
-          <t>6275021848</t>
+          <t>9671024201</t>
         </is>
       </c>
       <c r="G37" s="574" t="n"/>
@@ -28452,7 +28452,7 @@
       </c>
       <c r="I37" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="J37" s="579" t="inlineStr">
@@ -28462,7 +28462,7 @@
       </c>
       <c r="K37" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="L37" s="580" t="inlineStr">
@@ -28485,13 +28485,13 @@
         </is>
       </c>
       <c r="Q37" s="560" t="n">
-        <v>5645470779</v>
+        <v>3081835135</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C38" s="574" t="inlineStr">
@@ -28511,32 +28511,32 @@
       </c>
       <c r="F38" s="574" t="inlineStr">
         <is>
-          <t>6710242013</t>
+          <t>3480135499</t>
         </is>
       </c>
       <c r="G38" s="574" t="inlineStr">
         <is>
-          <t>08183</t>
+          <t>94489</t>
         </is>
       </c>
       <c r="H38" s="574" t="inlineStr">
         <is>
-          <t>5135348013</t>
+          <t>6418010423</t>
         </is>
       </c>
       <c r="I38" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="J38" s="574" t="inlineStr">
         <is>
-          <t>Refactoring portale istituzionale AlphaBank.it</t>
+          <t>Refactoring portale istituzionale tommaso.gentile</t>
         </is>
       </c>
       <c r="K38" s="579" t="inlineStr">
         <is>
-          <t>Martina Leone</t>
+          <t>Fabio Esposito</t>
         </is>
       </c>
       <c r="L38" s="580" t="inlineStr">
@@ -28559,7 +28559,7 @@
         </is>
       </c>
       <c r="Q38" s="560" t="n">
-        <v>4999448964</v>
+        <v>4303099463</v>
       </c>
       <c r="T38" s="580" t="n"/>
     </row>
@@ -28961,7 +28961,7 @@
     <row r="3">
       <c r="B3" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C3" s="574" t="inlineStr">
@@ -28991,22 +28991,22 @@
       </c>
       <c r="H3" s="574" t="inlineStr">
         <is>
-          <t>1801042394</t>
+          <t>0454805572</t>
         </is>
       </c>
       <c r="I3" s="574" t="inlineStr">
         <is>
-          <t>43030</t>
+          <t>05397</t>
         </is>
       </c>
       <c r="J3" s="574" t="inlineStr">
         <is>
-          <t>9946304548</t>
+          <t>5297628275</t>
         </is>
       </c>
       <c r="K3" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L3" s="579" t="inlineStr">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="M3" s="579" t="inlineStr">
         <is>
-          <t>Andrea Leone</t>
+          <t>Sara Russo</t>
         </is>
       </c>
       <c r="N3" s="580" t="inlineStr">
@@ -29034,13 +29034,13 @@
         <v>0</v>
       </c>
       <c r="R3" s="560" t="n">
-        <v>557205397</v>
+        <v>2913842566</v>
       </c>
     </row>
     <row r="4" ht="72.5" customHeight="1" s="564">
       <c r="B4" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C4" s="574" t="inlineStr">
@@ -29070,22 +29070,22 @@
       </c>
       <c r="H4" s="574" t="inlineStr">
         <is>
-          <t>5297628275</t>
+          <t>1948148911</t>
         </is>
       </c>
       <c r="I4" s="574" t="inlineStr">
         <is>
-          <t>29138</t>
+          <t>61326</t>
         </is>
       </c>
       <c r="J4" s="574" t="inlineStr">
         <is>
-          <t>4256619481</t>
+          <t>7576368147</t>
         </is>
       </c>
       <c r="K4" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L4" s="579" t="inlineStr">
@@ -29095,7 +29095,7 @@
       </c>
       <c r="M4" s="579" t="inlineStr">
         <is>
-          <t>Andrea Leone</t>
+          <t>Sara Russo</t>
         </is>
       </c>
       <c r="N4" s="580" t="inlineStr">
@@ -29131,7 +29131,7 @@
     <row r="5" ht="29" customHeight="1" s="564">
       <c r="B5" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C5" s="574" t="inlineStr">
@@ -29161,22 +29161,22 @@
       </c>
       <c r="H5" s="129" t="inlineStr">
         <is>
-          <t>4891161326</t>
+          <t>7494432373</t>
         </is>
       </c>
       <c r="I5" s="574" t="inlineStr">
         <is>
-          <t>75763</t>
+          <t>56398</t>
         </is>
       </c>
       <c r="J5" s="574" t="inlineStr">
         <is>
-          <t>6814774944</t>
+          <t>7018440244</t>
         </is>
       </c>
       <c r="K5" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L5" s="579" t="inlineStr">
@@ -29186,7 +29186,7 @@
       </c>
       <c r="M5" s="579" t="inlineStr">
         <is>
-          <t>Stefano Rinaldi</t>
+          <t>Aurora Santoro</t>
         </is>
       </c>
       <c r="N5" s="580" t="inlineStr">
@@ -29215,7 +29215,7 @@
     <row r="6">
       <c r="B6" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C6" s="574" t="inlineStr">
@@ -29245,22 +29245,22 @@
       </c>
       <c r="H6" s="129" t="inlineStr">
         <is>
-          <t>3237356398</t>
+          <t>4916887596</t>
         </is>
       </c>
       <c r="I6" s="574" t="inlineStr">
         <is>
-          <t>70184</t>
+          <t>94734</t>
         </is>
       </c>
       <c r="J6" s="574" t="inlineStr">
         <is>
-          <t>4024449168</t>
+          <t>3938895291</t>
         </is>
       </c>
       <c r="K6" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L6" s="579" t="inlineStr">
@@ -29288,7 +29288,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="560" t="n">
-        <v>8759694734</v>
+        <v>2740871165</v>
       </c>
       <c r="S6" s="579" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
     </row>
     <row r="7" ht="145" customHeight="1" s="564">
       <c r="B7" s="574" t="n">
-        <v>9915583648</v>
+        <v>9951761468</v>
       </c>
       <c r="C7" s="574" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
       </c>
       <c r="H7" s="574" t="inlineStr">
         <is>
-          <t>3938895291</t>
+          <t>5336033744</t>
         </is>
       </c>
       <c r="I7" s="574" t="n"/>
@@ -29338,7 +29338,7 @@
       </c>
       <c r="K7" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L7" s="579" t="inlineStr">
@@ -29348,7 +29348,7 @@
       </c>
       <c r="M7" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="N7" s="580" t="inlineStr">
@@ -29385,7 +29385,7 @@
     <row r="8" ht="29" customHeight="1" s="564">
       <c r="B8" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C8" s="574" t="inlineStr">
@@ -29415,7 +29415,7 @@
       </c>
       <c r="H8" s="574" t="inlineStr">
         <is>
-          <t>2740871165</t>
+          <t>7133903486</t>
         </is>
       </c>
       <c r="I8" s="129" t="n"/>
@@ -29427,7 +29427,7 @@
       </c>
       <c r="K8" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L8" s="579" t="inlineStr">
@@ -29437,7 +29437,7 @@
       </c>
       <c r="M8" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="N8" s="580" t="inlineStr">
@@ -29455,7 +29455,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="560" t="n">
-        <v>5336033744</v>
+        <v>2810442428</v>
       </c>
       <c r="S8" s="579" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
     <row r="9">
       <c r="B9" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C9" s="574" t="inlineStr">
@@ -29496,7 +29496,7 @@
       </c>
       <c r="H9" s="574" t="inlineStr">
         <is>
-          <t>7133903486</t>
+          <t>0901545409</t>
         </is>
       </c>
       <c r="I9" s="574" t="n"/>
@@ -29507,7 +29507,7 @@
       </c>
       <c r="K9" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -29517,7 +29517,7 @@
       </c>
       <c r="M9" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Romano</t>
+          <t>Andrea Ferrara</t>
         </is>
       </c>
       <c r="N9" s="580" t="inlineStr">
@@ -29535,7 +29535,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="560" t="n">
-        <v>8104424280</v>
+        <v>8051723345</v>
       </c>
       <c r="S9" s="579" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
     <row r="10" ht="28" customHeight="1" s="564">
       <c r="B10" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C10" s="574" t="inlineStr">
@@ -29576,22 +29576,22 @@
       </c>
       <c r="H10" s="574" t="inlineStr">
         <is>
-          <t>9015454092</t>
+          <t>2727953813</t>
         </is>
       </c>
       <c r="I10" s="574" t="inlineStr">
         <is>
-          <t>80517</t>
+          <t>22947</t>
         </is>
       </c>
       <c r="J10" s="574" t="inlineStr">
         <is>
-          <t>2334527279</t>
+          <t>3203571570</t>
         </is>
       </c>
       <c r="K10" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L10" s="579" t="inlineStr">
@@ -29601,7 +29601,7 @@
       </c>
       <c r="M10" s="579" t="inlineStr">
         <is>
-          <t>Simone Conti</t>
+          <t>Nicola Longo</t>
         </is>
       </c>
       <c r="N10" s="580" t="inlineStr">
@@ -29619,7 +29619,7 @@
         <v>0</v>
       </c>
       <c r="R10" s="560" t="n">
-        <v>8132294732</v>
+        <v>783293692</v>
       </c>
       <c r="S10" s="579" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
     <row r="11">
       <c r="B11" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C11" s="574" t="inlineStr">
@@ -29660,22 +29660,22 @@
       </c>
       <c r="H11" s="574" t="inlineStr">
         <is>
-          <t>0357157007</t>
+          <t>8027502166</t>
         </is>
       </c>
       <c r="I11" s="574" t="inlineStr">
         <is>
-          <t>83293</t>
+          <t>66922</t>
         </is>
       </c>
       <c r="J11" s="574" t="inlineStr">
         <is>
-          <t>6928027502</t>
+          <t>8119255966</t>
         </is>
       </c>
       <c r="K11" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L11" s="579" t="inlineStr">
@@ -29685,7 +29685,7 @@
       </c>
       <c r="M11" s="579" t="inlineStr">
         <is>
-          <t>Simone Conti</t>
+          <t>Nicola Longo</t>
         </is>
       </c>
       <c r="N11" s="580" t="inlineStr">
@@ -29703,7 +29703,7 @@
         <v>0</v>
       </c>
       <c r="R11" s="560" t="n">
-        <v>1666692281</v>
+        <v>9517743381</v>
       </c>
       <c r="S11" s="579" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
     <row r="12" ht="72.5" customHeight="1" s="564">
       <c r="B12" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C12" s="574" t="inlineStr">
@@ -29744,22 +29744,22 @@
       </c>
       <c r="H12" s="574" t="inlineStr">
         <is>
-          <t>1925596695</t>
+          <t>2010921186</t>
         </is>
       </c>
       <c r="I12" s="574" t="inlineStr">
         <is>
-          <t>17743</t>
+          <t>60867</t>
         </is>
       </c>
       <c r="J12" s="574" t="inlineStr">
         <is>
-          <t>3812010921</t>
+          <t>5527066250</t>
         </is>
       </c>
       <c r="K12" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L12" s="579" t="inlineStr">
@@ -29769,14 +29769,14 @@
       </c>
       <c r="M12" s="579" t="inlineStr">
         <is>
-          <t>Stefano Rinaldi</t>
+          <t>Aurora Santoro</t>
         </is>
       </c>
       <c r="N12" s="580" t="inlineStr">
         <is>
           <t>Fatturazione novembre 23.016,48
 fatturato a novembre su telco 23.016,48 €
-Ndc Interna da telco vs 9997412455 di
+Ndc Interna da telco vs 9978094862 di
 23.016,48 € a maggio
 fatturazione delta maggio 69049,44</t>
         </is>
@@ -29800,7 +29800,7 @@
     <row r="13">
       <c r="B13" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C13" s="574" t="inlineStr">
@@ -29830,22 +29830,22 @@
       </c>
       <c r="H13" s="574" t="inlineStr">
         <is>
-          <t>1866086755</t>
+          <t>1157490005</t>
         </is>
       </c>
       <c r="I13" s="574" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>86893</t>
         </is>
       </c>
       <c r="J13" s="574" t="inlineStr">
         <is>
-          <t>2501157490</t>
+          <t>8918975803</t>
         </is>
       </c>
       <c r="K13" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L13" s="579" t="inlineStr">
@@ -29855,7 +29855,7 @@
       </c>
       <c r="M13" s="579" t="inlineStr">
         <is>
-          <t>Luca Vitale</t>
+          <t>Valentina Santoro</t>
         </is>
       </c>
       <c r="N13" s="580" t="inlineStr">
@@ -29873,7 +29873,7 @@
         <v>0</v>
       </c>
       <c r="R13" s="560" t="n">
-        <v>58689389</v>
+        <v>5455544279</v>
       </c>
       <c r="S13" s="579" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
     <row r="14">
       <c r="B14" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C14" s="574" t="inlineStr">
@@ -29914,7 +29914,7 @@
       </c>
       <c r="H14" s="574" t="inlineStr">
         <is>
-          <t>1897580354</t>
+          <t>1277407831</t>
         </is>
       </c>
       <c r="I14" s="574" t="n"/>
@@ -29925,7 +29925,7 @@
       </c>
       <c r="K14" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L14" s="579" t="inlineStr">
@@ -29935,7 +29935,7 @@
       </c>
       <c r="M14" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="N14" s="580" t="inlineStr">
@@ -29953,13 +29953,13 @@
         <v>0</v>
       </c>
       <c r="R14" s="560" t="n">
-        <v>5554427912</v>
+        <v>80062912</v>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1" s="564">
       <c r="B15" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C15" s="223" t="inlineStr">
@@ -29989,7 +29989,7 @@
       </c>
       <c r="H15" s="574" t="inlineStr">
         <is>
-          <t>7740783100</t>
+          <t>4455404513</t>
         </is>
       </c>
       <c r="I15" s="226" t="n"/>
@@ -30000,7 +30000,7 @@
       </c>
       <c r="K15" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L15" s="579" t="inlineStr">
@@ -30010,7 +30010,7 @@
       </c>
       <c r="M15" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="N15" s="580" t="inlineStr">
@@ -30028,7 +30028,7 @@
         <v>0</v>
       </c>
       <c r="R15" s="560" t="n">
-        <v>8006291244</v>
+        <v>9183459380</v>
       </c>
       <c r="T15" s="580" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
     <row r="16" ht="87" customHeight="1" s="564">
       <c r="B16" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C16" s="223" t="inlineStr">
@@ -30069,7 +30069,7 @@
       </c>
       <c r="H16" s="574" t="inlineStr">
         <is>
-          <t>5540451391</t>
+          <t>7910701914</t>
         </is>
       </c>
       <c r="J16" s="574" t="inlineStr">
@@ -30079,7 +30079,7 @@
       </c>
       <c r="K16" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L16" s="579" t="inlineStr">
@@ -30089,7 +30089,7 @@
       </c>
       <c r="M16" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="N16" s="580" t="inlineStr">
@@ -30125,7 +30125,7 @@
     <row r="17">
       <c r="B17" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C17" s="223" t="inlineStr">
@@ -30155,20 +30155,20 @@
       </c>
       <c r="H17" s="574" t="inlineStr">
         <is>
-          <t>8345938079</t>
+          <t>8146546311</t>
         </is>
       </c>
       <c r="I17" s="574" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>44530</t>
         </is>
       </c>
       <c r="J17" s="560" t="n">
-        <v>9148146546</v>
+        <v>2561804089</v>
       </c>
       <c r="K17" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L17" s="560" t="inlineStr">
@@ -30196,7 +30196,7 @@
         <v>0</v>
       </c>
       <c r="R17" s="560" t="n">
-        <v>3114453025</v>
+        <v>8528340293</v>
       </c>
       <c r="S17" s="579" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
     <row r="18" ht="29" customHeight="1" s="564">
       <c r="B18" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C18" s="223" t="inlineStr">
@@ -30237,7 +30237,7 @@
       </c>
       <c r="H18" s="225" t="inlineStr">
         <is>
-          <t>6180408985</t>
+          <t>1025118179</t>
         </is>
       </c>
       <c r="I18" s="226" t="n"/>
@@ -30248,7 +30248,7 @@
       </c>
       <c r="K18" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L18" s="579" t="inlineStr">
@@ -30258,7 +30258,7 @@
       </c>
       <c r="M18" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="N18" s="579" t="inlineStr">
@@ -30290,7 +30290,7 @@
     <row r="19" ht="16" customHeight="1" s="564">
       <c r="B19" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C19" s="223" t="inlineStr">
@@ -30320,7 +30320,7 @@
       </c>
       <c r="H19" s="225" t="inlineStr">
         <is>
-          <t>2834029310</t>
+          <t>1727170414</t>
         </is>
       </c>
       <c r="I19" s="226" t="n"/>
@@ -30331,7 +30331,7 @@
       </c>
       <c r="K19" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L19" s="579" t="inlineStr">
@@ -30341,7 +30341,7 @@
       </c>
       <c r="M19" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="N19" s="579" t="inlineStr">
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="R19" s="560" t="n">
-        <v>2511817917</v>
+        <v>2849314905</v>
       </c>
       <c r="S19" s="579" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
     <row r="20">
       <c r="B20" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C20" s="223" t="inlineStr">
@@ -30400,7 +30400,7 @@
       </c>
       <c r="H20" s="574" t="inlineStr">
         <is>
-          <t>2717041428</t>
+          <t>1354909164</t>
         </is>
       </c>
       <c r="I20" s="574" t="n"/>
@@ -30411,7 +30411,7 @@
       </c>
       <c r="K20" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L20" s="579" t="inlineStr">
@@ -30421,7 +30421,7 @@
       </c>
       <c r="M20" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="N20" s="580" t="inlineStr">
@@ -30439,7 +30439,7 @@
         <v>0</v>
       </c>
       <c r="R20" s="560" t="n">
-        <v>4931490513</v>
+        <v>7547236971</v>
       </c>
       <c r="S20" s="579" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
     <row r="21">
       <c r="B21" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C21" s="574" t="inlineStr">
@@ -30480,22 +30480,22 @@
       </c>
       <c r="H21" s="574" t="inlineStr">
         <is>
-          <t>5490916475</t>
+          <t>8669419256</t>
         </is>
       </c>
       <c r="I21" s="574" t="inlineStr">
         <is>
-          <t>47236</t>
+          <t>09843</t>
         </is>
       </c>
       <c r="J21" s="574" t="inlineStr">
         <is>
-          <t>9718669419</t>
+          <t>6435216136</t>
         </is>
       </c>
       <c r="K21" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L21" s="579" t="inlineStr">
@@ -30505,7 +30505,7 @@
       </c>
       <c r="M21" s="579" t="inlineStr">
         <is>
-          <t>Stefano Rinaldi</t>
+          <t>Aurora Santoro</t>
         </is>
       </c>
       <c r="N21" s="580" t="inlineStr">
@@ -30536,7 +30536,7 @@
     <row r="22">
       <c r="B22" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C22" s="574" t="inlineStr">
@@ -30566,22 +30566,22 @@
       </c>
       <c r="H22" s="574" t="inlineStr">
         <is>
-          <t>2560984364</t>
+          <t>7835654095</t>
         </is>
       </c>
       <c r="I22" s="574" t="inlineStr">
         <is>
-          <t>35216</t>
+          <t>08732</t>
         </is>
       </c>
       <c r="J22" s="574" t="inlineStr">
         <is>
-          <t>1367835654</t>
+          <t>2582514019</t>
         </is>
       </c>
       <c r="K22" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L22" s="579" t="inlineStr">
@@ -30591,7 +30591,7 @@
       </c>
       <c r="M22" s="579" t="inlineStr">
         <is>
-          <t>Luca Gentile</t>
+          <t>Monica Colombo</t>
         </is>
       </c>
       <c r="N22" s="580" t="inlineStr">
@@ -30622,7 +30622,7 @@
     <row r="23" ht="72.5" customHeight="1" s="564">
       <c r="B23" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C23" s="574" t="inlineStr">
@@ -30652,22 +30652,22 @@
       </c>
       <c r="H23" s="574" t="inlineStr">
         <is>
-          <t>9508732258</t>
+          <t>8434147416</t>
         </is>
       </c>
       <c r="I23" s="574" t="inlineStr">
         <is>
-          <t>25140</t>
+          <t>36228</t>
         </is>
       </c>
       <c r="J23" s="574" t="inlineStr">
         <is>
-          <t>1984341474</t>
+          <t>6611771178</t>
         </is>
       </c>
       <c r="K23" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L23" s="579" t="inlineStr">
@@ -30677,7 +30677,7 @@
       </c>
       <c r="M23" s="579" t="inlineStr">
         <is>
-          <t>Andrea Leone</t>
+          <t>Sara Russo</t>
         </is>
       </c>
       <c r="N23" s="580" t="inlineStr">
@@ -30713,7 +30713,7 @@
     <row r="24" ht="29" customHeight="1" s="564">
       <c r="B24" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C24" s="574" t="inlineStr">
@@ -30743,7 +30743,7 @@
       </c>
       <c r="H24" s="574" t="inlineStr">
         <is>
-          <t>1636228661</t>
+          <t>5948142855</t>
         </is>
       </c>
       <c r="I24" s="574" t="n"/>
@@ -30754,7 +30754,7 @@
       </c>
       <c r="K24" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L24" s="579" t="inlineStr">
@@ -30764,7 +30764,7 @@
       </c>
       <c r="M24" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="N24" s="580" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="25" ht="29" customHeight="1" s="564">
       <c r="B25" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C25" s="574" t="inlineStr">
@@ -30826,22 +30826,22 @@
       </c>
       <c r="H25" s="574" t="inlineStr">
         <is>
-          <t>1771178594</t>
+          <t>7260961246</t>
         </is>
       </c>
       <c r="I25" s="574" t="inlineStr">
         <is>
-          <t>81428</t>
+          <t>78301</t>
         </is>
       </c>
       <c r="J25" s="574" t="inlineStr">
         <is>
-          <t>5572609612</t>
+          <t>0264330131</t>
         </is>
       </c>
       <c r="K25" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L25" s="579" t="inlineStr">
@@ -30851,7 +30851,7 @@
       </c>
       <c r="M25" s="579" t="inlineStr">
         <is>
-          <t>Elisa Caruso</t>
+          <t>Aurora Caruso</t>
         </is>
       </c>
       <c r="N25" s="580" t="inlineStr">
@@ -30885,7 +30885,7 @@
     <row r="26">
       <c r="B26" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C26" s="574" t="inlineStr">
@@ -30915,22 +30915,22 @@
       </c>
       <c r="H26" s="574" t="inlineStr">
         <is>
-          <t>4678301026</t>
+          <t>0756695204</t>
         </is>
       </c>
       <c r="I26" s="574" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="J26" s="574" t="inlineStr">
         <is>
-          <t>3107566952</t>
+          <t>5155462514</t>
         </is>
       </c>
       <c r="K26" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L26" s="579" t="inlineStr">
@@ -30940,7 +30940,7 @@
       </c>
       <c r="M26" s="579" t="inlineStr">
         <is>
-          <t>Marco Esposito</t>
+          <t>Serena Conti</t>
         </is>
       </c>
       <c r="N26" s="580" t="inlineStr">
@@ -30966,7 +30966,7 @@
     <row r="27">
       <c r="B27" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C27" s="574" t="inlineStr">
@@ -30996,7 +30996,7 @@
       </c>
       <c r="H27" s="574" t="inlineStr">
         <is>
-          <t>1255351554</t>
+          <t>3575014309</t>
         </is>
       </c>
       <c r="I27" s="574" t="n"/>
@@ -31007,7 +31007,7 @@
       </c>
       <c r="K27" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L27" s="579" t="inlineStr">
@@ -31017,7 +31017,7 @@
       </c>
       <c r="M27" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Romano</t>
+          <t>Andrea Ferrara</t>
         </is>
       </c>
       <c r="N27" s="580" t="inlineStr">
@@ -31035,7 +31035,7 @@
         <v>0</v>
       </c>
       <c r="R27" s="560" t="n">
-        <v>6251433575</v>
+        <v>3331987241</v>
       </c>
       <c r="S27" s="579" t="inlineStr">
         <is>
@@ -31046,7 +31046,7 @@
     <row r="28" ht="43.5" customHeight="1" s="564">
       <c r="B28" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C28" s="574" t="inlineStr">
@@ -31076,7 +31076,7 @@
       </c>
       <c r="H28" s="574" t="inlineStr">
         <is>
-          <t>0143093331</t>
+          <t>4804217955</t>
         </is>
       </c>
       <c r="I28" s="574" t="n"/>
@@ -31087,7 +31087,7 @@
       </c>
       <c r="K28" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L28" s="579" t="inlineStr">
@@ -31097,7 +31097,7 @@
       </c>
       <c r="M28" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="N28" s="580" t="n"/>
@@ -31122,7 +31122,7 @@
     <row r="29" ht="101.5" customHeight="1" s="564">
       <c r="B29" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C29" s="574" t="inlineStr">
@@ -31152,7 +31152,7 @@
       </c>
       <c r="H29" s="574" t="inlineStr">
         <is>
-          <t>9872414804</t>
+          <t>1770849816</t>
         </is>
       </c>
       <c r="I29" s="574" t="n"/>
@@ -31163,7 +31163,7 @@
       </c>
       <c r="K29" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L29" s="579" t="inlineStr">
@@ -31173,7 +31173,7 @@
       </c>
       <c r="M29" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="N29" s="580" t="n"/>
@@ -31206,7 +31206,7 @@
     <row r="30" ht="58" customHeight="1" s="564">
       <c r="B30" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C30" s="574" t="inlineStr">
@@ -31236,14 +31236,14 @@
       </c>
       <c r="H30" s="574" t="inlineStr">
         <is>
-          <t>2179551770</t>
+          <t>4406350313</t>
         </is>
       </c>
       <c r="I30" s="574" t="n"/>
       <c r="J30" s="574" t="n"/>
       <c r="K30" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L30" s="579" t="inlineStr">
@@ -31253,7 +31253,7 @@
       </c>
       <c r="M30" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="N30" s="606" t="n"/>
@@ -31283,7 +31283,7 @@
     <row r="31" ht="43.5" customHeight="1" s="564">
       <c r="B31" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C31" s="574" t="inlineStr">
@@ -31313,14 +31313,14 @@
       </c>
       <c r="H31" s="574" t="inlineStr">
         <is>
-          <t>8498164406</t>
+          <t>2130010797</t>
         </is>
       </c>
       <c r="I31" s="574" t="n"/>
       <c r="J31" s="574" t="n"/>
       <c r="K31" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L31" s="385" t="inlineStr">
@@ -31330,7 +31330,7 @@
       </c>
       <c r="M31" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Marino</t>
+          <t>Ilaria Romano</t>
         </is>
       </c>
       <c r="N31" s="606" t="n"/>
@@ -31619,7 +31619,7 @@
     <row r="3">
       <c r="B3" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C3" s="574" t="inlineStr">
@@ -31649,18 +31649,18 @@
       </c>
       <c r="H3" s="574" t="inlineStr">
         <is>
-          <t>3503132130</t>
+          <t>1626430124</t>
         </is>
       </c>
       <c r="I3" s="574" t="inlineStr">
         <is>
-          <t>01079</t>
+          <t>51068</t>
         </is>
       </c>
       <c r="J3" s="574" t="n"/>
       <c r="K3" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L3" s="365" t="inlineStr">
@@ -31670,7 +31670,7 @@
       </c>
       <c r="M3" s="579" t="inlineStr">
         <is>
-          <t>Marco Esposito</t>
+          <t>Serena Conti</t>
         </is>
       </c>
       <c r="N3" s="580" t="n"/>
@@ -31714,7 +31714,7 @@
       </c>
       <c r="H4" s="574" t="inlineStr">
         <is>
-          <t>7162643012</t>
+          <t>7035859750</t>
         </is>
       </c>
       <c r="I4" s="574" t="n"/>
@@ -31775,7 +31775,7 @@
       </c>
       <c r="H5" s="574" t="inlineStr">
         <is>
-          <t>4510687035</t>
+          <t>0677764824</t>
         </is>
       </c>
       <c r="I5" s="574" t="n"/>
@@ -31787,7 +31787,7 @@
       </c>
       <c r="M5" s="579" t="inlineStr">
         <is>
-          <t>Anna Santoro</t>
+          <t>Laura Ferrara</t>
         </is>
       </c>
       <c r="N5" s="606" t="n"/>
@@ -31831,7 +31831,7 @@
       </c>
       <c r="H6" s="574" t="inlineStr">
         <is>
-          <t>5975006777</t>
+          <t>6275016973</t>
         </is>
       </c>
       <c r="I6" s="574" t="n"/>
@@ -31843,7 +31843,7 @@
       </c>
       <c r="M6" s="579" t="inlineStr">
         <is>
-          <t>Anna Santoro</t>
+          <t>Laura Ferrara</t>
         </is>
       </c>
       <c r="N6" s="606" t="n"/>
@@ -31857,7 +31857,7 @@
     <row r="7">
       <c r="B7" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C7" s="574" t="inlineStr">
@@ -31887,19 +31887,19 @@
       </c>
       <c r="H7" s="574" t="inlineStr">
         <is>
-          <t>6482436275</t>
+          <t>7361164180</t>
         </is>
       </c>
       <c r="I7" s="574" t="n"/>
       <c r="J7" s="574" t="n"/>
       <c r="K7" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L7" s="579" t="inlineStr">
         <is>
-          <t>AlphaBank - Mythos Assessment Cyber.AI</t>
+          <t>AlphaBank - Mythos Assessment pietro.rizzo</t>
         </is>
       </c>
       <c r="N7" s="606" t="inlineStr">
@@ -31918,7 +31918,7 @@
     <row r="8">
       <c r="B8" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C8" s="574" t="inlineStr">
@@ -31948,14 +31948,14 @@
       </c>
       <c r="H8" s="574" t="inlineStr">
         <is>
-          <t>0169737361</t>
+          <t>2166137454</t>
         </is>
       </c>
       <c r="I8" s="574" t="n"/>
       <c r="J8" s="574" t="n"/>
       <c r="L8" s="579" t="inlineStr">
         <is>
-          <t>BetaCredit - Mythos Assessment Cyber.AI</t>
+          <t>BetaCredit - Mythos Assessment pietro.rizzo</t>
         </is>
       </c>
       <c r="N8" s="606" t="inlineStr">
@@ -31974,7 +31974,7 @@
     <row r="9" ht="29" customHeight="1" s="564">
       <c r="B9" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C9" s="574" t="inlineStr">
@@ -32004,14 +32004,14 @@
       </c>
       <c r="H9" s="574" t="inlineStr">
         <is>
-          <t>1641802166</t>
+          <t>8316543996</t>
         </is>
       </c>
       <c r="I9" s="574" t="n"/>
       <c r="J9" s="574" t="n"/>
       <c r="K9" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L9" s="579" t="inlineStr">
@@ -32035,7 +32035,7 @@
     <row r="10">
       <c r="B10" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C10" s="574" t="inlineStr">
@@ -32065,19 +32065,19 @@
       </c>
       <c r="H10" s="574" t="inlineStr">
         <is>
-          <t>1374548316</t>
+          <t>5075302982</t>
         </is>
       </c>
       <c r="I10" s="574" t="n"/>
       <c r="J10" s="574" t="n"/>
       <c r="K10" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L10" s="579" t="inlineStr">
         <is>
-          <t>BetaCredit_PMO SAST</t>
+          <t>Findo_PMO SAST</t>
         </is>
       </c>
       <c r="N10" s="606" t="inlineStr">
@@ -32096,7 +32096,7 @@
     <row r="11" ht="29" customHeight="1" s="564">
       <c r="B11" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C11" s="574" t="inlineStr">
@@ -32126,24 +32126,24 @@
       </c>
       <c r="H11" s="574" t="inlineStr">
         <is>
-          <t>5439965075</t>
+          <t>0321102991</t>
         </is>
       </c>
       <c r="I11" s="574" t="n"/>
       <c r="J11" s="574" t="n"/>
       <c r="K11" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L11" s="579" t="inlineStr">
         <is>
-          <t>Giorgio Conti</t>
+          <t>Valentina Leone</t>
         </is>
       </c>
       <c r="M11" s="579" t="inlineStr">
         <is>
-          <t>Riccardo Romano</t>
+          <t>Andrea Ferrara</t>
         </is>
       </c>
       <c r="N11" s="580" t="inlineStr">
@@ -32161,7 +32161,7 @@
     <row r="12" ht="58" customHeight="1" s="564">
       <c r="B12" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C12" s="574" t="inlineStr">
@@ -32191,7 +32191,7 @@
       </c>
       <c r="H12" s="574" t="inlineStr">
         <is>
-          <t>0298203211</t>
+          <t>1930233071</t>
         </is>
       </c>
       <c r="I12" s="574" t="n"/>
@@ -32203,7 +32203,7 @@
       </c>
       <c r="M12" s="579" t="inlineStr">
         <is>
-          <t>Elisa Caruso</t>
+          <t>Aurora Caruso</t>
         </is>
       </c>
       <c r="N12" s="580" t="inlineStr">
@@ -32251,14 +32251,14 @@
       </c>
       <c r="H13" s="574" t="inlineStr">
         <is>
-          <t>0299151930</t>
+          <t>9642737364</t>
         </is>
       </c>
       <c r="I13" s="574" t="n"/>
       <c r="J13" s="574" t="n"/>
       <c r="L13" s="579" t="inlineStr">
         <is>
-          <t>Cardif - Logos</t>
+          <t>SigmaInsure - Logos</t>
         </is>
       </c>
       <c r="N13" s="580" t="n"/>
@@ -32302,14 +32302,14 @@
       </c>
       <c r="H14" s="574" t="inlineStr">
         <is>
-          <t>2330719642</t>
+          <t>7355538786</t>
         </is>
       </c>
       <c r="I14" s="574" t="n"/>
       <c r="J14" s="574" t="n"/>
       <c r="L14" s="579" t="inlineStr">
         <is>
-          <t>Cardif - Cyber.AI</t>
+          <t>SigmaInsure - pietro.rizzo</t>
         </is>
       </c>
       <c r="N14" s="580" t="n"/>
@@ -32349,7 +32349,7 @@
       </c>
       <c r="H15" s="574" t="inlineStr">
         <is>
-          <t>7373647355</t>
+          <t>5071078850</t>
         </is>
       </c>
       <c r="I15" s="574" t="n"/>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="H16" s="574" t="inlineStr">
         <is>
-          <t>5387865071</t>
+          <t>1877259304</t>
         </is>
       </c>
       <c r="I16" s="574" t="n"/>
@@ -32417,7 +32417,7 @@
     <row r="17">
       <c r="B17" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C17" s="574" t="inlineStr">
@@ -32447,14 +32447,14 @@
       </c>
       <c r="H17" s="574" t="inlineStr">
         <is>
-          <t>0788501877</t>
+          <t>3529230550</t>
         </is>
       </c>
       <c r="I17" s="574" t="n"/>
       <c r="J17" s="574" t="n"/>
       <c r="K17" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L17" s="579" t="inlineStr">
@@ -32478,7 +32478,7 @@
     <row r="18">
       <c r="B18" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C18" s="574" t="inlineStr">
@@ -32508,14 +32508,14 @@
       </c>
       <c r="H18" s="574" t="inlineStr">
         <is>
-          <t>2593043529</t>
+          <t>2358867315</t>
         </is>
       </c>
       <c r="I18" s="574" t="n"/>
       <c r="J18" s="574" t="n"/>
       <c r="K18" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L18" s="579" t="inlineStr">
@@ -32539,7 +32539,7 @@
     <row r="19">
       <c r="B19" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C19" s="574" t="inlineStr">
@@ -32569,14 +32569,14 @@
       </c>
       <c r="H19" s="574" t="inlineStr">
         <is>
-          <t>2305502358</t>
+          <t>7334890313</t>
         </is>
       </c>
       <c r="I19" s="574" t="n"/>
       <c r="J19" s="574" t="n"/>
       <c r="K19" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L19" s="579" t="inlineStr">
@@ -32600,7 +32600,7 @@
     <row r="20">
       <c r="B20" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C20" s="574" t="inlineStr">
@@ -32630,14 +32630,14 @@
       </c>
       <c r="H20" s="574" t="inlineStr">
         <is>
-          <t>8673157334</t>
+          <t>7906828120</t>
         </is>
       </c>
       <c r="I20" s="574" t="n"/>
       <c r="J20" s="574" t="n"/>
       <c r="K20" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L20" s="579" t="inlineStr">
@@ -32661,7 +32661,7 @@
     <row r="21">
       <c r="B21" s="574" t="inlineStr">
         <is>
-          <t>9915583648</t>
+          <t>9951761468</t>
         </is>
       </c>
       <c r="C21" s="574" t="inlineStr">
@@ -32691,14 +32691,14 @@
       </c>
       <c r="H21" s="574" t="inlineStr">
         <is>
-          <t>8903137906</t>
+          <t>0275096288</t>
         </is>
       </c>
       <c r="I21" s="574" t="n"/>
       <c r="J21" s="574" t="n"/>
       <c r="K21" s="579" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="L21" s="579" t="inlineStr">
@@ -32722,7 +32722,7 @@
     <row r="22">
       <c r="B22" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C22" s="574" t="inlineStr">
@@ -32752,14 +32752,14 @@
       </c>
       <c r="H22" s="574" t="inlineStr">
         <is>
-          <t>8281200275</t>
+          <t>0278206535</t>
         </is>
       </c>
       <c r="I22" s="574" t="n"/>
       <c r="J22" s="574" t="n"/>
       <c r="K22" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L22" s="579" t="inlineStr">
@@ -32779,7 +32779,7 @@
     <row r="23">
       <c r="B23" s="574" t="inlineStr">
         <is>
-          <t>9997412455</t>
+          <t>9978094862</t>
         </is>
       </c>
       <c r="C23" s="574" t="inlineStr">
@@ -32814,7 +32814,7 @@
       <c r="J23" s="574" t="n"/>
       <c r="K23" s="579" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="L23" s="579" t="inlineStr">
@@ -32964,12 +32964,12 @@
       </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>9060013876</t>
+          <t>7317984193</t>
         </is>
       </c>
       <c r="E4" s="29" t="inlineStr">
         <is>
-          <t>CC1K9001</t>
+          <t>CQZBN001</t>
         </is>
       </c>
       <c r="F4" s="611" t="n">
@@ -33002,12 +33002,12 @@
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>1056828813</t>
+          <t>5791516980</t>
         </is>
       </c>
       <c r="E5" s="29" t="inlineStr">
         <is>
-          <t>C9DK4001</t>
+          <t>CJB17001</t>
         </is>
       </c>
       <c r="F5" s="611" t="n">
@@ -33041,12 +33041,12 @@
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>5783765539</t>
+          <t>0568288132</t>
         </is>
       </c>
       <c r="E6" s="29" t="inlineStr">
         <is>
-          <t>C7KAZ001</t>
+          <t>CYCIB001</t>
         </is>
       </c>
       <c r="F6" s="611" t="n">
@@ -33075,12 +33075,12 @@
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>6276192693</t>
+          <t>2966451835</t>
         </is>
       </c>
       <c r="E7" s="29" t="inlineStr">
         <is>
-          <t>CUOVQ001</t>
+          <t>C98OK001</t>
         </is>
       </c>
       <c r="F7" s="611" t="n">
@@ -33113,12 +33113,12 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>6032068609</t>
+          <t>8183023932</t>
         </is>
       </c>
       <c r="E8" s="29" t="inlineStr">
         <is>
-          <t>CIB98001</t>
+          <t>CYGN0001</t>
         </is>
       </c>
       <c r="F8" s="611" t="n">
@@ -33156,12 +33156,12 @@
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>5397945729</t>
+          <t>1313876218</t>
         </is>
       </c>
       <c r="E9" s="29" t="inlineStr">
         <is>
-          <t>COK6F001</t>
+          <t>C34R6001</t>
         </is>
       </c>
       <c r="F9" s="611" t="n">
@@ -33194,12 +33194,12 @@
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>7407719844</t>
+          <t>9062761926</t>
         </is>
       </c>
       <c r="E10" s="29" t="inlineStr">
         <is>
-          <t>C9MDI001</t>
+          <t>CM0OB001</t>
         </is>
       </c>
       <c r="F10" s="611" t="n">
@@ -33233,12 +33233,12 @@
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>3932613677</t>
+          <t>3560671270</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
         <is>
-          <t>CR6M0001</t>
+          <t>CK1UR001</t>
         </is>
       </c>
       <c r="F11" s="611" t="n">
@@ -33267,12 +33267,12 @@
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>9303560671</t>
+          <t>3654323749</t>
         </is>
       </c>
       <c r="E12" s="29" t="inlineStr">
         <is>
-          <t>CL5BK001</t>
+          <t>CFKKU001</t>
         </is>
       </c>
       <c r="F12" s="611" t="n">
@@ -33301,12 +33301,12 @@
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>6543654323</t>
+          <t>5664298817</t>
         </is>
       </c>
       <c r="E13" s="29" t="inlineStr">
         <is>
-          <t>C5RFK001</t>
+          <t>CZ8TE001</t>
         </is>
       </c>
       <c r="F13" s="611" t="n">
@@ -33352,12 +33352,12 @@
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>2556642988</t>
+          <t>6839290238</t>
         </is>
       </c>
       <c r="E14" s="29" t="inlineStr">
         <is>
-          <t>CF5Z8001</t>
+          <t>C1GFJ001</t>
         </is>
       </c>
       <c r="F14" s="611" t="n">
@@ -33410,12 +33410,12 @@
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>1387621824</t>
+          <t>2661596084</t>
         </is>
       </c>
       <c r="E15" s="29" t="inlineStr">
         <is>
-          <t>CTEY8001</t>
+          <t>CZ42O001</t>
         </is>
       </c>
       <c r="F15" s="611" t="n">
@@ -33454,7 +33454,7 @@
       </c>
       <c r="E16" s="29" t="inlineStr">
         <is>
-          <t>CMJCK001</t>
+          <t>CJ33Z001</t>
         </is>
       </c>
       <c r="F16" s="611" t="n">
@@ -33483,12 +33483,12 @@
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>38611269</t>
+          <t>55116726</t>
         </is>
       </c>
       <c r="E17" s="29" t="inlineStr">
         <is>
-          <t>C42O001</t>
+          <t>C55I001</t>
         </is>
       </c>
       <c r="F17" s="611" t="n">
@@ -33517,12 +33517,12 @@
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>9731624752</t>
+          <t>2044538361</t>
         </is>
       </c>
       <c r="E18" s="29" t="inlineStr">
         <is>
-          <t>CJ33Z001</t>
+          <t>CE940001</t>
         </is>
       </c>
       <c r="F18" s="611" t="n">
@@ -33558,12 +33558,12 @@
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>5511672677</t>
+          <t>9723870063</t>
         </is>
       </c>
       <c r="E19" s="29" t="inlineStr">
         <is>
-          <t>CIE94001</t>
+          <t>C643S001</t>
         </is>
       </c>
       <c r="F19" s="611" t="n">
@@ -33618,12 +33618,12 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>7788760317</t>
+          <t>9274305476</t>
         </is>
       </c>
       <c r="E20" s="29" t="inlineStr">
         <is>
-          <t>C04IP001</t>
+          <t>C4SX3001</t>
         </is>
       </c>
       <c r="F20" s="611" t="n">
@@ -33666,12 +33666,12 @@
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>3473395526</t>
+          <t>1300068553</t>
         </is>
       </c>
       <c r="E21" s="29" t="inlineStr">
         <is>
-          <t>C92BC001</t>
+          <t>CM2N4001</t>
         </is>
       </c>
       <c r="F21" s="611" t="n">
@@ -33711,12 +33711,12 @@
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>7300291503</t>
+          <t>8405386334</t>
         </is>
       </c>
       <c r="E22" s="29" t="inlineStr">
         <is>
-          <t>CYP64001</t>
+          <t>CMRB9001</t>
         </is>
       </c>
       <c r="F22" s="611" t="n">
@@ -33752,12 +33752,12 @@
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>5770968277</t>
+          <t>7887556341</t>
         </is>
       </c>
       <c r="E23" s="29" t="inlineStr">
         <is>
-          <t>C3S4S001</t>
+          <t>CNFQQ001</t>
         </is>
       </c>
       <c r="F23" s="611" t="n">
@@ -33797,12 +33797,12 @@
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>4554656210</t>
+          <t>5023778876</t>
         </is>
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>CX3M2001</t>
+          <t>C9R25001</t>
         </is>
       </c>
       <c r="F24" s="611" t="n">
@@ -33831,7 +33831,7 @@
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>3739408314</t>
+          <t>8697429304</t>
         </is>
       </c>
       <c r="E25" s="163" t="inlineStr">
@@ -33899,12 +33899,12 @@
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>7870950732</t>
+          <t>4726767434</t>
         </is>
       </c>
       <c r="E26" s="163" t="inlineStr">
         <is>
-          <t>CQ9R2001</t>
+          <t>CM225001</t>
         </is>
       </c>
       <c r="F26" s="611" t="n">
@@ -33943,12 +33943,12 @@
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>7869742930</t>
+          <t>0295876358</t>
         </is>
       </c>
       <c r="E27" s="29" t="inlineStr">
         <is>
-          <t>CQM22001</t>
+          <t>C5DSU001</t>
         </is>
       </c>
       <c r="F27" s="611" t="n">
@@ -33989,12 +33989,12 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>1801042394</t>
+          <t>0454805572</t>
         </is>
       </c>
       <c r="E28" s="29" t="inlineStr">
         <is>
-          <t>C5BLV001</t>
+          <t>CTG4W001</t>
         </is>
       </c>
       <c r="F28" s="611" t="n">
@@ -34029,12 +34029,12 @@
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>5297628275</t>
+          <t>1948148911</t>
         </is>
       </c>
       <c r="E29" s="29" t="inlineStr">
         <is>
-          <t>C95ZM001</t>
+          <t>CR4F2001</t>
         </is>
       </c>
       <c r="F29" s="611" t="n">
@@ -34087,12 +34087,12 @@
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>0547629300</t>
+          <t>3444723518</t>
         </is>
       </c>
       <c r="E30" s="29" t="inlineStr">
         <is>
-          <t>CX65D001</t>
+          <t>CL6YT001</t>
         </is>
       </c>
       <c r="F30" s="611" t="n">
@@ -34135,12 +34135,12 @@
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>4891161326</t>
+          <t>7494432373</t>
         </is>
       </c>
       <c r="E31" s="29" t="inlineStr">
         <is>
-          <t>CSUTG001</t>
+          <t>C3210001</t>
         </is>
       </c>
       <c r="F31" s="611" t="n">
@@ -34180,12 +34180,12 @@
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>0107302688</t>
+          <t>5336793687</t>
         </is>
       </c>
       <c r="E32" s="29" t="inlineStr">
         <is>
-          <t>C4WR4001</t>
+          <t>CQN53001</t>
         </is>
       </c>
       <c r="F32" s="611" t="n">
@@ -34228,12 +34228,12 @@
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>6710242013</t>
+          <t>3480135499</t>
         </is>
       </c>
       <c r="E33" s="29" t="inlineStr">
         <is>
-          <t>CF2L6001</t>
+          <t>CZ5PK001</t>
         </is>
       </c>
       <c r="F33" s="611" t="n">
@@ -34265,7 +34265,7 @@
       <c r="D34" s="5" t="n"/>
       <c r="E34" s="29" t="inlineStr">
         <is>
-          <t>CYT32001</t>
+          <t>CV9LO001</t>
         </is>
       </c>
       <c r="F34" s="611" t="n">
@@ -34306,12 +34306,12 @@
       </c>
       <c r="D35" s="20" t="inlineStr">
         <is>
-          <t>3367936873</t>
+          <t>9224297388</t>
         </is>
       </c>
       <c r="E35" s="29" t="inlineStr">
         <is>
-          <t>C10QN001</t>
+          <t>CXAFX001</t>
         </is>
       </c>
       <c r="F35" s="611" t="n">
@@ -34354,12 +34354,12 @@
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>2544658114</t>
+          <t>9010730268</t>
         </is>
       </c>
       <c r="E36" s="29" t="inlineStr">
         <is>
-          <t>C53Z5001</t>
+          <t>CUNW9001</t>
         </is>
       </c>
       <c r="F36" s="611" t="n">
@@ -34397,12 +34397,12 @@
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>7133903486</t>
+          <t>0901545409</t>
         </is>
       </c>
       <c r="E37" s="29" t="inlineStr">
         <is>
-          <t>CPKV9001</t>
+          <t>CIF44001</t>
         </is>
       </c>
       <c r="F37" s="611" t="n">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>3938895291</t>
+          <t>5336033744</t>
         </is>
       </c>
       <c r="E38" s="29" t="inlineStr">
         <is>
-          <t>CLOXA001</t>
+          <t>CVKPB001</t>
         </is>
       </c>
       <c r="F38" s="611" t="n">
@@ -34483,12 +34483,12 @@
       </c>
       <c r="D39" s="20" t="inlineStr">
         <is>
-          <t>9015454092</t>
+          <t>2727953813</t>
         </is>
       </c>
       <c r="E39" s="29" t="inlineStr">
         <is>
-          <t>CFXUN001</t>
+          <t>C9584001</t>
         </is>
       </c>
       <c r="F39" s="611" t="n">
@@ -34526,12 +34526,12 @@
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>0357157007</t>
+          <t>8027502166</t>
         </is>
       </c>
       <c r="E40" s="29" t="inlineStr">
         <is>
-          <t>CW9IF001</t>
+          <t>CR5MF001</t>
         </is>
       </c>
       <c r="F40" s="611" t="n">
@@ -34562,12 +34562,12 @@
       </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t>1925596695</t>
+          <t>2010921186</t>
         </is>
       </c>
       <c r="E41" s="29" t="inlineStr">
         <is>
-          <t>C44VK001</t>
+          <t>C0O03001</t>
         </is>
       </c>
       <c r="F41" s="611" t="n">
@@ -34607,12 +34607,12 @@
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>1897580354</t>
+          <t>1277407831</t>
         </is>
       </c>
       <c r="E42" s="29" t="inlineStr">
         <is>
-          <t>CPB95001</t>
+          <t>CS1R7001</t>
         </is>
       </c>
       <c r="F42" s="611" t="n">
@@ -34641,22 +34641,22 @@
     <row r="43" hidden="1" ht="261" customHeight="1" s="564">
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Cardif</t>
+          <t>SigmaInsure</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Application Security Test Cardif</t>
+          <t>Application Security Test SigmaInsure</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
         <is>
-          <t>87479316</t>
+          <t>81848213</t>
         </is>
       </c>
       <c r="E43" s="29" t="inlineStr">
         <is>
-          <t>CO03S001</t>
+          <t>CK9FW001</t>
         </is>
       </c>
       <c r="F43" s="611" t="n">
@@ -34714,7 +34714,7 @@
       </c>
       <c r="E44" s="29" t="inlineStr">
         <is>
-          <t>C1R76001</t>
+          <t>CZBBD001</t>
         </is>
       </c>
       <c r="F44" s="611" t="n">
@@ -34751,12 +34751,12 @@
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
-          <t>1866086755</t>
+          <t>1157490005</t>
         </is>
       </c>
       <c r="E45" s="29" t="inlineStr">
         <is>
-          <t>CF8T6001</t>
+          <t>CSM6K001</t>
         </is>
       </c>
       <c r="F45" s="611" t="n">
@@ -34799,12 +34799,12 @@
       </c>
       <c r="D46" s="251" t="inlineStr">
         <is>
-          <t>5540451391</t>
+          <t>7910701914</t>
         </is>
       </c>
       <c r="E46" s="277" t="inlineStr">
         <is>
-          <t>CLGNK001</t>
+          <t>CWU47001</t>
         </is>
       </c>
       <c r="F46" s="617" t="n">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="D47" s="251" t="inlineStr">
         <is>
-          <t>3237356398</t>
+          <t>4916887596</t>
         </is>
       </c>
       <c r="E47" s="29" t="inlineStr">
         <is>
-          <t>C9FWZ001</t>
+          <t>CV2YL001</t>
         </is>
       </c>
       <c r="F47" s="611" t="n">
@@ -34886,12 +34886,12 @@
       </c>
       <c r="D48" s="251" t="inlineStr">
         <is>
-          <t>8345938079</t>
+          <t>8146546311</t>
         </is>
       </c>
       <c r="E48" s="29" t="inlineStr">
         <is>
-          <t>CBBDS001</t>
+          <t>CZVE8001</t>
         </is>
       </c>
       <c r="F48" s="611" t="n">
@@ -34930,12 +34930,12 @@
       </c>
       <c r="D49" s="251" t="inlineStr">
         <is>
-          <t>6180408985</t>
+          <t>1025118179</t>
         </is>
       </c>
       <c r="E49" s="163" t="inlineStr">
         <is>
-          <t>CM6KW001</t>
+          <t>C0UBS001</t>
         </is>
       </c>
       <c r="F49" s="611" t="n">
@@ -34973,12 +34973,12 @@
       </c>
       <c r="D50" s="251" t="inlineStr">
         <is>
-          <t>2740871165</t>
+          <t>7133903486</t>
         </is>
       </c>
       <c r="E50" s="29" t="inlineStr">
         <is>
-          <t>CU47V001</t>
+          <t>C5WGU001</t>
         </is>
       </c>
       <c r="F50" s="611" t="n">
@@ -35016,12 +35016,12 @@
       </c>
       <c r="D51" s="20" t="inlineStr">
         <is>
-          <t>2834029310</t>
+          <t>1727170414</t>
         </is>
       </c>
       <c r="E51" s="289" t="inlineStr">
         <is>
-          <t>C2YLZ001</t>
+          <t>CA29J001</t>
         </is>
       </c>
       <c r="F51" s="611" t="n">
@@ -35060,12 +35060,12 @@
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>51865904</t>
+          <t>51814857</t>
         </is>
       </c>
       <c r="E52" s="29" t="inlineStr">
         <is>
-          <t>C5WGU001</t>
+          <t>CN1KH001</t>
         </is>
       </c>
       <c r="F52" s="611" t="n">
@@ -35099,17 +35099,17 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>25-140RFP F.U. RUN ProdSec &amp; Sistemi</t>
+          <t>25-140RFP nicola.longo RUN ProdSec &amp; Sistemi</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
         <is>
-          <t>0782518148</t>
+          <t>6520678377</t>
         </is>
       </c>
       <c r="E53" s="29" t="inlineStr">
         <is>
-          <t>CX3N1001</t>
+          <t>CMTEV001</t>
         </is>
       </c>
       <c r="F53" s="611" t="n">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>21652067</t>
+          <t>03235424</t>
         </is>
       </c>
       <c r="E54" s="29" t="inlineStr">
         <is>
-          <t>C7O22001</t>
+          <t>CEH4A001</t>
         </is>
       </c>
       <c r="F54" s="611" t="n">
@@ -35182,7 +35182,7 @@
       <c r="J54" s="32" t="inlineStr">
         <is>
           <t>131, 52 Ambrosi 4h gennaio rilasci siteminder
-324,82 daniele guerra febbraio
+324,82 Ilaria Ferrari febbraio
 272,60 Guerra Trasferta Feb + 112
 56 Diaria trasferta Ruggiero marzo</t>
         </is>
@@ -35204,12 +35204,12 @@
       </c>
       <c r="D55" s="20" t="inlineStr">
         <is>
-          <t>34195032</t>
+          <t>50230220</t>
         </is>
       </c>
       <c r="E55" s="29" t="inlineStr">
         <is>
-          <t>COWSJ001</t>
+          <t>CROS4001</t>
         </is>
       </c>
       <c r="F55" s="611" t="n">
@@ -35247,12 +35247,12 @@
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>9508732258</t>
+          <t>8434147416</t>
         </is>
       </c>
       <c r="E56" s="29" t="inlineStr">
         <is>
-          <t>CQEH4001</t>
+          <t>CD6IJ001</t>
         </is>
       </c>
       <c r="F56" s="611" t="n">
@@ -35296,7 +35296,7 @@
       </c>
       <c r="E57" s="29" t="inlineStr">
         <is>
-          <t>CAXBL001</t>
+          <t>CROYC001</t>
         </is>
       </c>
       <c r="F57" s="611" t="n">
@@ -35340,7 +35340,7 @@
       </c>
       <c r="E58" s="29" t="inlineStr">
         <is>
-          <t>CMCJJ001</t>
+          <t>CU4AU001</t>
         </is>
       </c>
       <c r="F58" s="611" t="n">
@@ -35382,7 +35382,7 @@
       </c>
       <c r="E59" s="29" t="inlineStr">
         <is>
-          <t>CBROS001</t>
+          <t>CZO7Z001</t>
         </is>
       </c>
       <c r="F59" s="611" t="n">
@@ -35426,7 +35426,7 @@
       </c>
       <c r="E60" s="29" t="inlineStr">
         <is>
-          <t>C4D6I001</t>
+          <t>COFYF001</t>
         </is>
       </c>
       <c r="F60" s="611" t="n">
@@ -35468,7 +35468,7 @@
       </c>
       <c r="E61" s="29" t="inlineStr">
         <is>
-          <t>CJROY001</t>
+          <t>CSRWR001</t>
         </is>
       </c>
       <c r="F61" s="611" t="n">
@@ -35509,7 +35509,7 @@
       </c>
       <c r="E62" s="29" t="inlineStr">
         <is>
-          <t>CCU4A001</t>
+          <t>CAZVG001</t>
         </is>
       </c>
       <c r="F62" s="611" t="n">
@@ -35549,7 +35549,7 @@
       </c>
       <c r="E63" s="29" t="inlineStr">
         <is>
-          <t>CUZO7001</t>
+          <t>CT5NE001</t>
         </is>
       </c>
       <c r="F63" s="611" t="n">
@@ -35590,7 +35590,7 @@
       </c>
       <c r="E64" s="29" t="inlineStr">
         <is>
-          <t>CZOFY001</t>
+          <t>CCCKY001</t>
         </is>
       </c>
       <c r="F64" s="611" t="n">
@@ -35633,7 +35633,7 @@
       </c>
       <c r="E65" s="29" t="inlineStr">
         <is>
-          <t>CFSRW001</t>
+          <t>C4POW001</t>
         </is>
       </c>
       <c r="F65" s="611" t="n">
@@ -35668,7 +35668,7 @@
       </c>
       <c r="C66" s="567" t="inlineStr">
         <is>
-          <t>Add on servizio ZetaGroup_2</t>
+          <t>Add on servizio EACB_2</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
@@ -35676,7 +35676,7 @@
       </c>
       <c r="E66" s="29" t="inlineStr">
         <is>
-          <t>CRAZV001</t>
+          <t>CBACG001</t>
         </is>
       </c>
       <c r="F66" s="611" t="n">
@@ -35706,7 +35706,7 @@
     <row r="67" hidden="1" ht="29" customHeight="1" s="564">
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Cardif</t>
+          <t>SigmaInsure</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -35719,7 +35719,7 @@
       </c>
       <c r="E67" s="29" t="inlineStr">
         <is>
-          <t>CGT5N001</t>
+          <t>CPPPM001</t>
         </is>
       </c>
       <c r="F67" s="611" t="n">
@@ -35761,7 +35761,7 @@
       </c>
       <c r="E68" s="289" t="inlineStr">
         <is>
-          <t>CECCK001</t>
+          <t>C4V12001</t>
         </is>
       </c>
       <c r="F68" s="611" t="n">
@@ -35795,7 +35795,7 @@
       </c>
       <c r="C69" s="567" t="inlineStr">
         <is>
-          <t>AlphaBank - Mythos Assessment Cyber.AI</t>
+          <t>AlphaBank - Mythos Assessment pietro.rizzo</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
@@ -35803,7 +35803,7 @@
       </c>
       <c r="E69" s="289" t="inlineStr">
         <is>
-          <t>CY4PO001</t>
+          <t>CNAQB001</t>
         </is>
       </c>
       <c r="F69" s="611" t="n">
@@ -35846,7 +35846,7 @@
       </c>
       <c r="E70" s="289" t="inlineStr">
         <is>
-          <t>CWBAC001</t>
+          <t>C3L7F001</t>
         </is>
       </c>
       <c r="F70" s="611" t="n">
@@ -35881,7 +35881,7 @@
       </c>
       <c r="C71" s="567" t="inlineStr">
         <is>
-          <t>BetaCredit - Mythos Assessment Cyber.AI</t>
+          <t>BetaCredit - Mythos Assessment pietro.rizzo</t>
         </is>
       </c>
       <c r="D71" s="3" t="n">
@@ -35889,7 +35889,7 @@
       </c>
       <c r="E71" s="567" t="inlineStr">
         <is>
-          <t>CGPPP001</t>
+          <t>CRIU0001</t>
         </is>
       </c>
       <c r="F71" s="611" t="n">
@@ -35929,7 +35929,7 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>CM4V1001</t>
+          <t>CCLXC001</t>
         </is>
       </c>
       <c r="F72" s="611" t="n">
@@ -35970,7 +35970,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>BetaCredit_PMO SAST</t>
+          <t>Findo_PMO SAST</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
@@ -35978,7 +35978,7 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>C2NAQ001</t>
+          <t>C8UA1001</t>
         </is>
       </c>
       <c r="F73" s="611" t="n">
@@ -36010,7 +36010,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Giorgio Conti</t>
+          <t>Valentina Leone</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
@@ -36018,7 +36018,7 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>CB3L7001</t>
+          <t>COK5U001</t>
         </is>
       </c>
       <c r="F74" s="611" t="n">
@@ -36052,7 +36052,7 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>CFRIU001</t>
+          <t>CLU9E001</t>
         </is>
       </c>
       <c r="F75" s="611" t="n">
@@ -36073,12 +36073,12 @@
     <row r="76">
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Cardif</t>
+          <t>SigmaInsure</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Cardif - Logos</t>
+          <t>SigmaInsure - Logos</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
@@ -36086,7 +36086,7 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>C0CLX001</t>
+          <t>CD4UX001</t>
         </is>
       </c>
       <c r="F76" s="611" t="n">
@@ -36107,12 +36107,12 @@
     <row r="77">
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Cardif</t>
+          <t>SigmaInsure</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Cardif - Cyber.AI</t>
+          <t>SigmaInsure - pietro.rizzo</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
@@ -36120,7 +36120,7 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>CC8UA001</t>
+          <t>CNDAH001</t>
         </is>
       </c>
       <c r="F77" s="611" t="n">
@@ -36154,7 +36154,7 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>C1OK5001</t>
+          <t>CMJ2W001</t>
         </is>
       </c>
       <c r="F78" s="611" t="n">
@@ -36188,7 +36188,7 @@
       </c>
       <c r="E79" s="567" t="inlineStr">
         <is>
-          <t>CULU9001</t>
+          <t>CQ6MW001</t>
         </is>
       </c>
       <c r="F79" s="611" t="n">
@@ -36372,7 +36372,7 @@
       </c>
       <c r="E85" s="567" t="inlineStr">
         <is>
-          <t>CED4U001</t>
+          <t>CIOCY001</t>
         </is>
       </c>
       <c r="F85" s="611" t="n">
@@ -37242,7 +37242,7 @@
     <row r="5">
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>martina.costa</t>
+          <t>silvia.esposito</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -37397,7 +37397,7 @@
     <row r="6">
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>matteo.costa</t>
+          <t>noemi.rossi</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -37606,7 +37606,7 @@
     <row r="7" ht="14.15" customHeight="1" s="564">
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>nicola.fontana</t>
+          <t>noemi.longo</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -37815,7 +37815,7 @@
     <row r="8">
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>luca.leone</t>
+          <t>roberto.bianchi</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -38014,7 +38014,7 @@
     <row r="9">
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>alberto lotito</t>
+          <t>Elena Costa</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -38223,7 +38223,7 @@
     <row r="10" ht="13.5" customHeight="1" s="564">
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>serena.rossi</t>
+          <t>gabriele.gentile</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -38432,7 +38432,7 @@
     <row r="11" ht="15" customHeight="1" s="564">
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>sara.colombo</t>
+          <t>pietro.mariani</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -38641,7 +38641,7 @@
     <row r="12">
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>matteo.romano</t>
+          <t>laura.longo</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -38850,7 +38850,7 @@
     <row r="13">
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>stefano.greco</t>
+          <t>nicola.ferrari</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -39051,7 +39051,7 @@
     <row r="14">
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>ilaria.esposito</t>
+          <t>elena.mariani</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -39240,7 +39240,7 @@
     <row r="15">
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>laura.moretti</t>
+          <t>ilaria.fontana</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -39429,7 +39429,7 @@
     <row r="16">
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>anna.ferrari</t>
+          <t>andrea.russo</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -39616,7 +39616,7 @@
     <row r="17">
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>roberto.costa</t>
+          <t>gabriele.fontana</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -39799,7 +39799,7 @@
     <row r="18">
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>paolo.greco</t>
+          <t>antonio.santoro</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -39958,7 +39958,7 @@
     <row r="19">
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>riccardo.gentile</t>
+          <t>noemi.rinaldi</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -40135,7 +40135,7 @@
     <row r="20">
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>fabio.ferrara</t>
+          <t>valentina.martini</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -40312,7 +40312,7 @@
     <row r="21" ht="16" customHeight="1" s="564">
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>serena.mariani</t>
+          <t>ilaria.longo</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
@@ -40469,7 +40469,7 @@
     <row r="22">
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>andrea.conti</t>
+          <t>ilaria.ferrari</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -40626,7 +40626,7 @@
     <row r="23" ht="13.5" customHeight="1" s="564">
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>anna.bianchi</t>
+          <t>monica.mariani</t>
         </is>
       </c>
       <c r="C23" s="250" t="n">
@@ -41033,7 +41033,7 @@
     <row r="28">
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>Spazio costi Massimo Silvestri - Formazione</t>
+          <t>Spazio costi Noemi Rinaldi - Formazione</t>
         </is>
       </c>
       <c r="C28" s="261" t="n">
@@ -42080,7 +42080,7 @@
     <row r="41" hidden="1" s="564">
       <c r="B41" s="311" t="inlineStr">
         <is>
-          <t>Alberto Russo</t>
+          <t>Sara Ferrari</t>
         </is>
       </c>
       <c r="C41" s="593" t="n">
@@ -42134,7 +42134,7 @@
     <row r="42" hidden="1" s="564">
       <c r="B42" s="567" t="inlineStr">
         <is>
-          <t>Alberto Russo</t>
+          <t>Sara Ferrari</t>
         </is>
       </c>
       <c r="C42" s="593" t="n">
@@ -43180,7 +43180,7 @@
     <row r="56">
       <c r="B56" s="290" t="inlineStr">
         <is>
-          <t>BetaCredit_PMO SAST</t>
+          <t>Findo_PMO SAST</t>
         </is>
       </c>
       <c r="C56" s="596" t="n">
@@ -43241,7 +43241,7 @@
     <row r="57">
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Giorgio Conti</t>
+          <t>Valentina Leone</t>
         </is>
       </c>
       <c r="C57" s="673" t="n">
@@ -44014,12 +44014,12 @@
       </c>
       <c r="B4" s="696" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="C4" s="696" t="inlineStr">
         <is>
-          <t>BFBZ3001</t>
+          <t>BBZ3U001</t>
         </is>
       </c>
       <c r="D4" s="688" t="n"/>
@@ -44177,12 +44177,12 @@
       </c>
       <c r="B5" s="696" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="C5" s="696" t="inlineStr">
         <is>
-          <t>BU7R5001</t>
+          <t>B7R5Y001</t>
         </is>
       </c>
       <c r="D5" s="688" t="n"/>
@@ -44971,11 +44971,11 @@
         </is>
       </c>
       <c r="D10" s="36" t="n">
-        <v>9915583648</v>
+        <v>9951761468</v>
       </c>
       <c r="E10" s="35" t="inlineStr">
         <is>
-          <t>BJRYD001</t>
+          <t>BV28N001</t>
         </is>
       </c>
       <c r="F10" s="35" t="inlineStr">
@@ -45983,11 +45983,11 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>9997412455</v>
+        <v>9978094862</v>
       </c>
       <c r="E17" s="35" t="inlineStr">
         <is>
-          <t>BGTY8001</t>
+          <t>BRWUF001</t>
         </is>
       </c>
       <c r="F17" s="35" t="inlineStr">
@@ -47022,7 +47022,7 @@
       <c r="D24" s="36" t="n"/>
       <c r="E24" s="35" t="inlineStr">
         <is>
-          <t>BYSOX001</t>
+          <t>BSOXG001</t>
         </is>
       </c>
       <c r="F24" s="191" t="inlineStr">
